--- a/DATA_AUDIT.xlsx
+++ b/DATA_AUDIT.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'validators'!$A$1:$H$229</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'self-audit'!$A$1:$I$581</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'self-audit'!$A$1:$I$601</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'funnel'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'basis'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'basis'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>PASS 8/8</t>
+          <t>PASS 12/12</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1988,16 +1988,24 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>PASS 1/1</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2431,7 +2439,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>PASS 4/7 - 3 FAIL</t>
+          <t>PASS 3/8 - 5 FAIL</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2468,16 +2476,24 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>PASS 1/1</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2675,7 +2691,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>PASS 5/11 - 1 FAIL - 5 input(s) not on this machine</t>
+          <t>PASS 13/15 - 2 FAIL</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2712,16 +2728,24 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>PASS 1/1</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3887,7 +3911,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>PASS 10/13 - 3 FAIL</t>
+          <t>PASS 12/15 - 3 FAIL</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5823,7 +5847,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/7 - 7 input(s) not on this machine</t>
+          <t>PASS 5/5</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
@@ -5852,16 +5876,24 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 input(s) not on this machine</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 COULD NOT RUN</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7263,7 +7295,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>PASS 10/10</t>
+          <t>PASS 11/11</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
@@ -7292,16 +7324,24 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>PASS 1/1</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -7499,7 +7539,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/7 - 7 input(s) not on this machine</t>
+          <t>PASS 5/5</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
@@ -7528,16 +7568,24 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 input(s) not on this machine</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 COULD NOT RUN</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7735,7 +7783,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>PASS 6/6</t>
+          <t>PASS 9/9</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
@@ -7971,7 +8019,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>PASS 14/15 - 1 input(s) not on this machine</t>
+          <t>PASS 16/16</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
@@ -8000,16 +8048,24 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>PASS 1/1</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -8076,16 +8132,24 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>PASS 4/4</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr"/>
+          <t>PASS 2/4 - 2 FAIL</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -9583,7 +9647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I581"/>
+  <dimension ref="A1:I601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14427,7 +14491,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -14437,14 +14501,22 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
+          <t>2 found</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>the config, currency_unit</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
+        </is>
+      </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["CNY billion", "yuan"]</t>
         </is>
       </c>
     </row>
@@ -15564,32 +15636,24 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>229 row(s)</t>
+          <t>190 row(s)</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>9 duplicate key(s)</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>calcs, funding_by_program</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>a programme-year counted twice is a union key collision: check budget_row_id suffixes in budget_rows.csv</t>
-        </is>
-      </c>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>["FY2015 head 1 programme 1.10 appears 2 times", "FY2015 head 1 programme 1.2 appears 2 times", "FY2015 head 1 programme 1.3 appears 2 times", "FY2015 head 1 programme 1.4 appears 2 times", "FY2015 head 1 programme 1.5 appears 2 times", "FY2015 head 1 programme 1.6 appears 2 times", "FY2015 head 1 programme 1.7 appears 2 times", "FY2015 head 1 programme 1.8 appears 2 times"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -15616,7 +15680,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>279 strategy-year(s)</t>
+          <t>146 strategy-year(s)</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -16304,24 +16368,32 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>13 row(s)</t>
+          <t>1362 row(s)</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>0 duplicate key(s)</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr"/>
+          <t>67 duplicate key(s)</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>calcs, funding_by_program</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>a programme-year counted twice is a union key collision: check budget_row_id suffixes in budget_rows.csv</t>
+        </is>
+      </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["FY2024 head 101 programme 101.1 appears 2 times", "FY2024 head 101 programme 101.3 appears 2 times", "FY2024 head 10 programme 10.1 appears 2 times", "FY2024 head 12 programme 12.1 appears 2 times", "FY2024 head 18 programme 18.01 appears 2 times", "FY2024 head 1 programme 1.1 appears 2 times", "FY2024 head 25 programme 25.01 appears 5 times", "FY2024 head 26 programme 26.01 appears 8 times"]</t>
         </is>
       </c>
     </row>
@@ -16348,7 +16420,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>1 strategy-year(s)</t>
+          <t>299 strategy-year(s)</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -22051,7 +22123,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -22082,7 +22154,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -22113,7 +22185,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -22128,11 +22200,19 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E344" s="2" t="inlineStr"/>
-      <c r="F344" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>482 row(s)</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
       <c r="G344" s="2" t="inlineStr"/>
       <c r="H344" s="2" t="inlineStr"/>
       <c r="I344" s="2" t="inlineStr">
@@ -22144,7 +22224,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -22159,11 +22239,19 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E345" s="2" t="inlineStr"/>
-      <c r="F345" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>91 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>0 over ceiling</t>
+        </is>
+      </c>
       <c r="G345" s="2" t="inlineStr"/>
       <c r="H345" s="2" t="inlineStr"/>
       <c r="I345" s="2" t="inlineStr">
@@ -22175,7 +22263,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -22206,7 +22294,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -22237,7 +22325,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -22268,7 +22356,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -22299,7 +22387,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -22330,7 +22418,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -22361,7 +22449,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -22392,7 +22480,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -22431,7 +22519,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -22462,7 +22550,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -22501,7 +22589,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -22532,7 +22620,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -22563,7 +22651,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -22594,7 +22682,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -22625,7 +22713,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -22656,7 +22744,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -22687,7 +22775,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -22702,19 +22790,11 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E362" s="2" t="inlineStr">
-        <is>
-          <t>22 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F362" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr"/>
+      <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr"/>
       <c r="H362" s="2" t="inlineStr"/>
       <c r="I362" s="2" t="inlineStr">
@@ -22726,7 +22806,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -22741,19 +22821,11 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E363" s="2" t="inlineStr">
-        <is>
-          <t>22 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F363" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr"/>
+      <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr"/>
       <c r="H363" s="2" t="inlineStr"/>
       <c r="I363" s="2" t="inlineStr">
@@ -22765,7 +22837,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -22780,19 +22852,11 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E364" s="2" t="inlineStr">
-        <is>
-          <t>159 row(s)</t>
-        </is>
-      </c>
-      <c r="F364" s="2" t="inlineStr">
-        <is>
-          <t>0 duplicate key(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr"/>
+      <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr"/>
       <c r="H364" s="2" t="inlineStr"/>
       <c r="I364" s="2" t="inlineStr">
@@ -22804,7 +22868,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -22819,19 +22883,11 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="inlineStr">
-        <is>
-          <t>104 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F365" s="2" t="inlineStr">
-        <is>
-          <t>0 over ceiling</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr"/>
+      <c r="F365" s="2" t="inlineStr"/>
       <c r="G365" s="2" t="inlineStr"/>
       <c r="H365" s="2" t="inlineStr"/>
       <c r="I365" s="2" t="inlineStr">
@@ -22843,7 +22899,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -22858,19 +22914,11 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E366" s="2" t="inlineStr">
-        <is>
-          <t>89 strategy-year figure(s)</t>
-        </is>
-      </c>
-      <c r="F366" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr"/>
+      <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr"/>
       <c r="H366" s="2" t="inlineStr"/>
       <c r="I366" s="2" t="inlineStr">
@@ -22882,7 +22930,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -22913,7 +22961,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -22928,19 +22976,11 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>89 strategyclean row(s)</t>
-        </is>
-      </c>
-      <c r="F368" s="2" t="inlineStr">
-        <is>
-          <t>89 panel row(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr"/>
+      <c r="F368" s="2" t="inlineStr"/>
       <c r="G368" s="2" t="inlineStr"/>
       <c r="H368" s="2" t="inlineStr"/>
       <c r="I368" s="2" t="inlineStr">
@@ -22952,7 +22992,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -22983,7 +23023,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -22998,19 +23038,11 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>855 distinct id(s)</t>
-        </is>
-      </c>
-      <c r="F370" s="2" t="inlineStr">
-        <is>
-          <t>0 dangle</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr"/>
+      <c r="F370" s="2" t="inlineStr"/>
       <c r="G370" s="2" t="inlineStr"/>
       <c r="H370" s="2" t="inlineStr"/>
       <c r="I370" s="2" t="inlineStr">
@@ -23022,7 +23054,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -23037,19 +23069,11 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>1 metric(s)</t>
-        </is>
-      </c>
-      <c r="F371" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr"/>
+      <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr"/>
       <c r="H371" s="2" t="inlineStr"/>
       <c r="I371" s="2" t="inlineStr">
@@ -23061,7 +23085,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -23092,7 +23116,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -23117,7 +23141,7 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
+          <t>0 found</t>
         </is>
       </c>
       <c r="G373" s="2" t="inlineStr"/>
@@ -23131,7 +23155,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -23146,19 +23170,11 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr">
-        <is>
-          <t>0 component(s)</t>
-        </is>
-      </c>
-      <c r="F374" s="2" t="inlineStr">
-        <is>
-          <t>0 untraceable</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr"/>
+      <c r="F374" s="2" t="inlineStr"/>
       <c r="G374" s="2" t="inlineStr"/>
       <c r="H374" s="2" t="inlineStr"/>
       <c r="I374" s="2" t="inlineStr">
@@ -23170,7 +23186,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -23209,7 +23225,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -23224,19 +23240,11 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E376" s="2" t="inlineStr">
-        <is>
-          <t>89 strategy(ies)</t>
-        </is>
-      </c>
-      <c r="F376" s="2" t="inlineStr">
-        <is>
-          <t>0 with no component</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr"/>
+      <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr"/>
       <c r="H376" s="2" t="inlineStr"/>
       <c r="I376" s="2" t="inlineStr">
@@ -23248,7 +23256,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -23279,7 +23287,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -23294,19 +23302,11 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>48 programme(s)</t>
-        </is>
-      </c>
-      <c r="F378" s="2" t="inlineStr">
-        <is>
-          <t>0 unreadable (0%), carrying 0% of the money</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr"/>
+      <c r="F378" s="2" t="inlineStr"/>
       <c r="G378" s="2" t="inlineStr"/>
       <c r="H378" s="2" t="inlineStr"/>
       <c r="I378" s="2" t="inlineStr">
@@ -23318,7 +23318,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -23349,7 +23349,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -23364,31 +23364,23 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>867 intervention(s) extracted</t>
-        </is>
-      </c>
-      <c r="F380" s="2" t="inlineStr">
-        <is>
-          <t>12 uncited (1.4%)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr"/>
+      <c r="F380" s="2" t="inlineStr"/>
       <c r="G380" s="2" t="inlineStr"/>
       <c r="H380" s="2" t="inlineStr"/>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>["207", "210", "272", "314", "421", "422", "431", "434"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -23419,7 +23411,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -23439,7 +23431,7 @@
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>22 strategy-year(s)</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -23458,7 +23450,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -23478,7 +23470,7 @@
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>22 strategy-year(s)</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -23497,7 +23489,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -23517,7 +23509,7 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>74 row(s)</t>
+          <t>159 row(s)</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -23536,7 +23528,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -23556,7 +23548,7 @@
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>104 strategy-year(s)</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -23575,7 +23567,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -23595,7 +23587,7 @@
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>106 strategy-year figure(s)</t>
+          <t>89 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
@@ -23614,7 +23606,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -23645,7 +23637,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -23665,12 +23657,12 @@
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>106 strategyclean row(s)</t>
+          <t>89 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>106 panel row(s)</t>
+          <t>89 panel row(s)</t>
         </is>
       </c>
       <c r="G388" s="2" t="inlineStr"/>
@@ -23684,7 +23676,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -23715,7 +23707,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -23735,7 +23727,7 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>617 distinct id(s)</t>
+          <t>855 distinct id(s)</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
@@ -23754,7 +23746,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -23793,7 +23785,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -23824,7 +23816,7 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -23863,7 +23855,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -23902,7 +23894,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -23941,7 +23933,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -23961,7 +23953,7 @@
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>106 strategy(ies)</t>
+          <t>89 strategy(ies)</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
@@ -23980,7 +23972,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -24011,7 +24003,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -24031,7 +24023,7 @@
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>74 programme(s)</t>
+          <t>48 programme(s)</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
@@ -24050,7 +24042,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -24081,7 +24073,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -24101,26 +24093,26 @@
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>617 intervention(s) extracted</t>
+          <t>867 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>0 uncited (0.0%)</t>
+          <t>12 uncited (1.4%)</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr"/>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["207", "210", "272", "314", "421", "422", "431", "434"]</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -24151,7 +24143,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -24171,7 +24163,7 @@
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>83 strategy-year(s)</t>
+          <t>11 strategy-year(s)</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -24190,7 +24182,7 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -24210,7 +24202,7 @@
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>83 strategy-year(s)</t>
+          <t>11 strategy-year(s)</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
@@ -24229,7 +24221,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -24249,7 +24241,7 @@
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>143 row(s)</t>
+          <t>74 row(s)</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -24268,7 +24260,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -24288,7 +24280,7 @@
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>36 strategy-year(s)</t>
+          <t>11 strategy-year(s)</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
@@ -24307,7 +24299,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -24327,7 +24319,7 @@
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year figure(s)</t>
+          <t>106 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -24346,7 +24338,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -24377,7 +24369,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -24397,12 +24389,12 @@
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>28 strategyclean row(s)</t>
+          <t>106 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>28 panel row(s)</t>
+          <t>106 panel row(s)</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr"/>
@@ -24416,7 +24408,7 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -24447,7 +24439,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -24467,7 +24459,7 @@
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>140 distinct id(s)</t>
+          <t>617 distinct id(s)</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -24486,7 +24478,7 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -24525,7 +24517,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -24556,7 +24548,7 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -24595,7 +24587,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -24634,7 +24626,7 @@
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -24673,7 +24665,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -24693,7 +24685,7 @@
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>28 strategy(ies)</t>
+          <t>106 strategy(ies)</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr">
@@ -24712,7 +24704,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -24743,7 +24735,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -24763,7 +24755,7 @@
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>191 programme(s)</t>
+          <t>74 programme(s)</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
@@ -24782,7 +24774,7 @@
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -24813,7 +24805,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -24833,7 +24825,7 @@
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>140 intervention(s) extracted</t>
+          <t>617 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
@@ -24852,7 +24844,7 @@
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -24883,7 +24875,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -24898,11 +24890,19 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E422" s="2" t="inlineStr"/>
-      <c r="F422" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>83 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G422" s="2" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr"/>
       <c r="I422" s="2" t="inlineStr">
@@ -24914,7 +24914,7 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -24929,11 +24929,19 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E423" s="2" t="inlineStr"/>
-      <c r="F423" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>83 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G423" s="2" t="inlineStr"/>
       <c r="H423" s="2" t="inlineStr"/>
       <c r="I423" s="2" t="inlineStr">
@@ -24945,7 +24953,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -24960,11 +24968,19 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E424" s="2" t="inlineStr"/>
-      <c r="F424" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>143 row(s)</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
       <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr"/>
       <c r="I424" s="2" t="inlineStr">
@@ -24976,7 +24992,7 @@
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -24991,11 +25007,19 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E425" s="2" t="inlineStr"/>
-      <c r="F425" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>36 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>0 over ceiling</t>
+        </is>
+      </c>
       <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr"/>
       <c r="I425" s="2" t="inlineStr">
@@ -25007,7 +25031,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -25022,11 +25046,19 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E426" s="2" t="inlineStr"/>
-      <c r="F426" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>28 strategy-year figure(s)</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr"/>
       <c r="I426" s="2" t="inlineStr">
@@ -25038,7 +25070,7 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -25069,7 +25101,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -25084,11 +25116,19 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E428" s="2" t="inlineStr"/>
-      <c r="F428" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>28 strategyclean row(s)</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>28 panel row(s)</t>
+        </is>
+      </c>
       <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr"/>
       <c r="I428" s="2" t="inlineStr">
@@ -25100,7 +25140,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -25131,7 +25171,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -25146,11 +25186,19 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E430" s="2" t="inlineStr"/>
-      <c r="F430" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>140 distinct id(s)</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>0 dangle</t>
+        </is>
+      </c>
       <c r="G430" s="2" t="inlineStr"/>
       <c r="H430" s="2" t="inlineStr"/>
       <c r="I430" s="2" t="inlineStr">
@@ -25162,7 +25210,7 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -25177,11 +25225,19 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E431" s="2" t="inlineStr"/>
-      <c r="F431" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>1 metric(s)</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G431" s="2" t="inlineStr"/>
       <c r="H431" s="2" t="inlineStr"/>
       <c r="I431" s="2" t="inlineStr">
@@ -25193,7 +25249,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -25224,7 +25280,7 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -25249,7 +25305,7 @@
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>0 found</t>
+          <t>1 found</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr"/>
@@ -25263,7 +25319,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -25278,11 +25334,19 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E434" s="2" t="inlineStr"/>
-      <c r="F434" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>0 component(s)</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>0 untraceable</t>
+        </is>
+      </c>
       <c r="G434" s="2" t="inlineStr"/>
       <c r="H434" s="2" t="inlineStr"/>
       <c r="I434" s="2" t="inlineStr">
@@ -25294,7 +25358,7 @@
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -25333,7 +25397,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -25348,11 +25412,19 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr"/>
-      <c r="F436" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>28 strategy(ies)</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>0 with no component</t>
+        </is>
+      </c>
       <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="2" t="inlineStr"/>
       <c r="I436" s="2" t="inlineStr">
@@ -25364,7 +25436,7 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -25395,7 +25467,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -25410,11 +25482,19 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr"/>
-      <c r="F438" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>191 programme(s)</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>0 unreadable (0%), carrying 0% of the money</t>
+        </is>
+      </c>
       <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr"/>
       <c r="I438" s="2" t="inlineStr">
@@ -25426,7 +25506,7 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -25457,7 +25537,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -25472,11 +25552,19 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E440" s="2" t="inlineStr"/>
-      <c r="F440" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>140 intervention(s) extracted</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>0 uncited (0.0%)</t>
+        </is>
+      </c>
       <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="2" t="inlineStr"/>
       <c r="I440" s="2" t="inlineStr">
@@ -25488,7 +25576,7 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -25519,7 +25607,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -25534,19 +25622,11 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E442" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F442" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr"/>
+      <c r="F442" s="2" t="inlineStr"/>
       <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr"/>
       <c r="I442" s="2" t="inlineStr">
@@ -25558,7 +25638,7 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -25573,19 +25653,11 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F443" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr"/>
+      <c r="F443" s="2" t="inlineStr"/>
       <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr"/>
       <c r="I443" s="2" t="inlineStr">
@@ -25597,7 +25669,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -25617,7 +25689,7 @@
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>140 row(s)</t>
+          <t>83 row(s)</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
@@ -25636,7 +25708,7 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -25656,7 +25728,7 @@
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>6 strategy-year(s)</t>
+          <t>8 strategy-year(s)</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
@@ -25675,7 +25747,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -25690,19 +25762,11 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>143 strategy-year figure(s)</t>
-        </is>
-      </c>
-      <c r="F446" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr"/>
+      <c r="F446" s="2" t="inlineStr"/>
       <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr"/>
       <c r="I446" s="2" t="inlineStr">
@@ -25714,7 +25778,7 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -25745,7 +25809,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -25760,19 +25824,11 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>143 strategyclean row(s)</t>
-        </is>
-      </c>
-      <c r="F448" s="2" t="inlineStr">
-        <is>
-          <t>143 panel row(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr"/>
+      <c r="F448" s="2" t="inlineStr"/>
       <c r="G448" s="2" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr"/>
       <c r="I448" s="2" t="inlineStr">
@@ -25784,7 +25840,7 @@
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -25815,7 +25871,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -25830,19 +25886,11 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E450" s="2" t="inlineStr">
-        <is>
-          <t>957 distinct id(s)</t>
-        </is>
-      </c>
-      <c r="F450" s="2" t="inlineStr">
-        <is>
-          <t>0 dangle</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr"/>
+      <c r="F450" s="2" t="inlineStr"/>
       <c r="G450" s="2" t="inlineStr"/>
       <c r="H450" s="2" t="inlineStr"/>
       <c r="I450" s="2" t="inlineStr">
@@ -25854,7 +25902,7 @@
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -25869,19 +25917,11 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E451" s="2" t="inlineStr">
-        <is>
-          <t>1 metric(s)</t>
-        </is>
-      </c>
-      <c r="F451" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr"/>
+      <c r="F451" s="2" t="inlineStr"/>
       <c r="G451" s="2" t="inlineStr"/>
       <c r="H451" s="2" t="inlineStr"/>
       <c r="I451" s="2" t="inlineStr">
@@ -25893,7 +25933,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -25924,7 +25964,7 @@
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -25939,7 +25979,7 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
@@ -25949,29 +25989,21 @@
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>2 found</t>
-        </is>
-      </c>
-      <c r="G453" s="2" t="inlineStr">
-        <is>
-          <t>the config, currency_unit</t>
-        </is>
-      </c>
-      <c r="H453" s="2" t="inlineStr">
-        <is>
-          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
-        </is>
-      </c>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr"/>
+      <c r="H453" s="2" t="inlineStr"/>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>["Rs. Billion", "Rs.Mn"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -25986,19 +26018,11 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>0 component(s)</t>
-        </is>
-      </c>
-      <c r="F454" s="2" t="inlineStr">
-        <is>
-          <t>0 untraceable</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr"/>
+      <c r="F454" s="2" t="inlineStr"/>
       <c r="G454" s="2" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr"/>
       <c r="I454" s="2" t="inlineStr">
@@ -26010,7 +26034,7 @@
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -26049,7 +26073,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -26064,19 +26088,11 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E456" s="2" t="inlineStr">
-        <is>
-          <t>143 strategy(ies)</t>
-        </is>
-      </c>
-      <c r="F456" s="2" t="inlineStr">
-        <is>
-          <t>0 with no component</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr"/>
+      <c r="F456" s="2" t="inlineStr"/>
       <c r="G456" s="2" t="inlineStr"/>
       <c r="H456" s="2" t="inlineStr"/>
       <c r="I456" s="2" t="inlineStr">
@@ -26088,7 +26104,7 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -26119,7 +26135,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -26150,7 +26166,7 @@
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -26181,7 +26197,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
@@ -26196,31 +26212,23 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E460" s="2" t="inlineStr">
-        <is>
-          <t>958 intervention(s) extracted</t>
-        </is>
-      </c>
-      <c r="F460" s="2" t="inlineStr">
-        <is>
-          <t>1 uncited (0.1%)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr"/>
+      <c r="F460" s="2" t="inlineStr"/>
       <c r="G460" s="2" t="inlineStr"/>
       <c r="H460" s="2" t="inlineStr"/>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>["2205"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -26251,7 +26259,7 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -26271,7 +26279,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year(s)</t>
+          <t>50 strategy-year(s)</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
@@ -26290,7 +26298,7 @@
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -26310,7 +26318,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year(s)</t>
+          <t>50 strategy-year(s)</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -26329,7 +26337,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -26349,7 +26357,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>324 row(s)</t>
+          <t>140 row(s)</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -26368,7 +26376,7 @@
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -26388,7 +26396,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>130 strategy-year(s)</t>
+          <t>6 strategy-year(s)</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -26407,7 +26415,7 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -26427,7 +26435,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>99 strategy-year figure(s)</t>
+          <t>143 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -26446,7 +26454,7 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -26477,7 +26485,7 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -26497,12 +26505,12 @@
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>99 strategyclean row(s)</t>
+          <t>143 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>99 panel row(s)</t>
+          <t>143 panel row(s)</t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr"/>
@@ -26516,7 +26524,7 @@
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -26547,7 +26555,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -26567,7 +26575,7 @@
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>525 distinct id(s)</t>
+          <t>957 distinct id(s)</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
@@ -26586,7 +26594,7 @@
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -26625,7 +26633,7 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -26656,7 +26664,7 @@
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -26671,7 +26679,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -26681,21 +26689,29 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
-        </is>
-      </c>
-      <c r="G473" s="2" t="inlineStr"/>
-      <c r="H473" s="2" t="inlineStr"/>
+          <t>2 found</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>the config, currency_unit</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
+        </is>
+      </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Rs. Billion", "Rs.Mn"]</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -26734,7 +26750,7 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -26773,7 +26789,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -26793,7 +26809,7 @@
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>99 strategy(ies)</t>
+          <t>143 strategy(ies)</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -26812,7 +26828,7 @@
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -26843,7 +26859,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -26858,19 +26874,11 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E478" s="2" t="inlineStr">
-        <is>
-          <t>273 programme(s)</t>
-        </is>
-      </c>
-      <c r="F478" s="2" t="inlineStr">
-        <is>
-          <t>0 unreadable (0%), carrying 0% of the money</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr"/>
+      <c r="F478" s="2" t="inlineStr"/>
       <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr"/>
       <c r="I478" s="2" t="inlineStr">
@@ -26882,7 +26890,7 @@
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -26913,7 +26921,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -26933,26 +26941,26 @@
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>533 intervention(s) extracted</t>
+          <t>958 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>8 uncited (1.5%)</t>
+          <t>1 uncited (0.1%)</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr"/>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>["202", "369", "383", "452", "472", "497", "503", "771"]</t>
+          <t>["2205"]</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -26983,7 +26991,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -27003,7 +27011,7 @@
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>2 strategy-year(s)</t>
+          <t>28 strategy-year(s)</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
@@ -27022,7 +27030,7 @@
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -27042,7 +27050,7 @@
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>2 strategy-year(s)</t>
+          <t>28 strategy-year(s)</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr">
@@ -27061,7 +27069,7 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -27076,31 +27084,39 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>17 row(s)</t>
+          <t>900 row(s)</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>0 duplicate key(s)</t>
-        </is>
-      </c>
-      <c r="G484" s="2" t="inlineStr"/>
-      <c r="H484" s="2" t="inlineStr"/>
+          <t>65 duplicate key(s)</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>calcs, funding_by_program</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>a programme-year counted twice is a union key collision: check budget_row_id suffixes in budget_rows.csv</t>
+        </is>
+      </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["FY2022 head 1 programme 1.1 appears 2 times", "FY2022 head 2 programme 2.2 appears 2 times", "FY2022 head 3 programme 3.3 appears 2 times", "FY2022 head 4 programme 4.4 appears 2 times", "FY2022 head 5 programme 5.5 appears 2 times", "FY2022 head 6 programme 6.6 appears 2 times", "FY2024 head 1 programme 1.1 appears 2 times", "FY2024 head 2 programme 2.2 appears 2 times"]</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -27120,7 +27136,7 @@
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>2 strategy-year(s)</t>
+          <t>165 strategy-year(s)</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -27139,7 +27155,7 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -27159,7 +27175,7 @@
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>6 strategy-year figure(s)</t>
+          <t>99 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
@@ -27178,7 +27194,7 @@
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -27209,7 +27225,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -27229,12 +27245,12 @@
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>6 strategyclean row(s)</t>
+          <t>99 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>6 panel row(s)</t>
+          <t>99 panel row(s)</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr"/>
@@ -27248,7 +27264,7 @@
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -27279,7 +27295,7 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -27299,7 +27315,7 @@
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>4 distinct id(s)</t>
+          <t>525 distinct id(s)</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
@@ -27318,7 +27334,7 @@
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -27357,7 +27373,7 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -27388,7 +27404,7 @@
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -27427,7 +27443,7 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -27466,7 +27482,7 @@
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -27505,7 +27521,7 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -27525,7 +27541,7 @@
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>6 strategy(ies)</t>
+          <t>99 strategy(ies)</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
@@ -27544,7 +27560,7 @@
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -27575,7 +27591,7 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -27595,7 +27611,7 @@
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>17 programme(s)</t>
+          <t>273 programme(s)</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
@@ -27614,7 +27630,7 @@
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -27645,7 +27661,7 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -27665,26 +27681,26 @@
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>4 intervention(s) extracted</t>
+          <t>533 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>0 uncited (0.0%)</t>
+          <t>8 uncited (1.5%)</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr"/>
       <c r="H500" s="2" t="inlineStr"/>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["202", "369", "383", "452", "472", "497", "503", "771"]</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -27715,7 +27731,7 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -27730,11 +27746,19 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E502" s="2" t="inlineStr"/>
-      <c r="F502" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>2 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G502" s="2" t="inlineStr"/>
       <c r="H502" s="2" t="inlineStr"/>
       <c r="I502" s="2" t="inlineStr">
@@ -27746,7 +27770,7 @@
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -27761,11 +27785,19 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E503" s="2" t="inlineStr"/>
-      <c r="F503" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>2 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G503" s="2" t="inlineStr"/>
       <c r="H503" s="2" t="inlineStr"/>
       <c r="I503" s="2" t="inlineStr">
@@ -27777,7 +27809,7 @@
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -27792,11 +27824,19 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr"/>
-      <c r="F504" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>17 row(s)</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
       <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr"/>
       <c r="I504" s="2" t="inlineStr">
@@ -27808,7 +27848,7 @@
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -27823,11 +27863,19 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E505" s="2" t="inlineStr"/>
-      <c r="F505" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>2 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>0 over ceiling</t>
+        </is>
+      </c>
       <c r="G505" s="2" t="inlineStr"/>
       <c r="H505" s="2" t="inlineStr"/>
       <c r="I505" s="2" t="inlineStr">
@@ -27839,7 +27887,7 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -27854,11 +27902,19 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E506" s="2" t="inlineStr"/>
-      <c r="F506" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>6 strategy-year figure(s)</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G506" s="2" t="inlineStr"/>
       <c r="H506" s="2" t="inlineStr"/>
       <c r="I506" s="2" t="inlineStr">
@@ -27870,7 +27926,7 @@
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -27901,7 +27957,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -27916,11 +27972,19 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E508" s="2" t="inlineStr"/>
-      <c r="F508" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>6 strategyclean row(s)</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>6 panel row(s)</t>
+        </is>
+      </c>
       <c r="G508" s="2" t="inlineStr"/>
       <c r="H508" s="2" t="inlineStr"/>
       <c r="I508" s="2" t="inlineStr">
@@ -27932,7 +27996,7 @@
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -27963,7 +28027,7 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
@@ -27978,11 +28042,19 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E510" s="2" t="inlineStr"/>
-      <c r="F510" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>4 distinct id(s)</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>0 dangle</t>
+        </is>
+      </c>
       <c r="G510" s="2" t="inlineStr"/>
       <c r="H510" s="2" t="inlineStr"/>
       <c r="I510" s="2" t="inlineStr">
@@ -27994,7 +28066,7 @@
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
@@ -28009,11 +28081,19 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E511" s="2" t="inlineStr"/>
-      <c r="F511" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>1 metric(s)</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G511" s="2" t="inlineStr"/>
       <c r="H511" s="2" t="inlineStr"/>
       <c r="I511" s="2" t="inlineStr">
@@ -28025,7 +28105,7 @@
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
@@ -28056,7 +28136,7 @@
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
@@ -28081,7 +28161,7 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>0 found</t>
+          <t>1 found</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr"/>
@@ -28095,7 +28175,7 @@
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
@@ -28110,11 +28190,19 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E514" s="2" t="inlineStr"/>
-      <c r="F514" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>0 component(s)</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>0 untraceable</t>
+        </is>
+      </c>
       <c r="G514" s="2" t="inlineStr"/>
       <c r="H514" s="2" t="inlineStr"/>
       <c r="I514" s="2" t="inlineStr">
@@ -28126,7 +28214,7 @@
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
@@ -28165,7 +28253,7 @@
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
@@ -28180,11 +28268,19 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E516" s="2" t="inlineStr"/>
-      <c r="F516" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>6 strategy(ies)</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>0 with no component</t>
+        </is>
+      </c>
       <c r="G516" s="2" t="inlineStr"/>
       <c r="H516" s="2" t="inlineStr"/>
       <c r="I516" s="2" t="inlineStr">
@@ -28196,7 +28292,7 @@
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
@@ -28227,7 +28323,7 @@
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
@@ -28242,11 +28338,19 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr"/>
-      <c r="F518" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>17 programme(s)</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>0 unreadable (0%), carrying 0% of the money</t>
+        </is>
+      </c>
       <c r="G518" s="2" t="inlineStr"/>
       <c r="H518" s="2" t="inlineStr"/>
       <c r="I518" s="2" t="inlineStr">
@@ -28258,7 +28362,7 @@
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
@@ -28289,7 +28393,7 @@
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
@@ -28304,11 +28408,19 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E520" s="2" t="inlineStr"/>
-      <c r="F520" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>4 intervention(s) extracted</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>0 uncited (0.0%)</t>
+        </is>
+      </c>
       <c r="G520" s="2" t="inlineStr"/>
       <c r="H520" s="2" t="inlineStr"/>
       <c r="I520" s="2" t="inlineStr">
@@ -28320,7 +28432,7 @@
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
@@ -28351,7 +28463,7 @@
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
@@ -28382,7 +28494,7 @@
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -28413,7 +28525,7 @@
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
@@ -28444,7 +28556,7 @@
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -28475,7 +28587,7 @@
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
@@ -28506,7 +28618,7 @@
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B527" s="2" t="inlineStr">
@@ -28537,7 +28649,7 @@
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B528" s="2" t="inlineStr">
@@ -28568,7 +28680,7 @@
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B529" s="2" t="inlineStr">
@@ -28599,7 +28711,7 @@
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
@@ -28630,7 +28742,7 @@
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
@@ -28661,7 +28773,7 @@
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
@@ -28692,7 +28804,7 @@
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -28731,7 +28843,7 @@
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
@@ -28762,7 +28874,7 @@
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
@@ -28801,7 +28913,7 @@
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
@@ -28832,7 +28944,7 @@
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
@@ -28863,7 +28975,7 @@
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
@@ -28894,7 +29006,7 @@
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
@@ -28925,7 +29037,7 @@
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
@@ -28956,7 +29068,7 @@
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B541" s="2" t="inlineStr">
@@ -28987,7 +29099,7 @@
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B542" s="2" t="inlineStr">
@@ -29018,7 +29130,7 @@
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B543" s="2" t="inlineStr">
@@ -29049,7 +29161,7 @@
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
@@ -29080,7 +29192,7 @@
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
@@ -29111,7 +29223,7 @@
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
@@ -29142,7 +29254,7 @@
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B547" s="2" t="inlineStr">
@@ -29173,7 +29285,7 @@
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B548" s="2" t="inlineStr">
@@ -29204,7 +29316,7 @@
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B549" s="2" t="inlineStr">
@@ -29235,7 +29347,7 @@
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
@@ -29266,7 +29378,7 @@
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -29297,7 +29409,7 @@
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B552" s="2" t="inlineStr">
@@ -29328,7 +29440,7 @@
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
@@ -29367,7 +29479,7 @@
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
@@ -29398,7 +29510,7 @@
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B555" s="2" t="inlineStr">
@@ -29437,7 +29549,7 @@
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
@@ -29468,7 +29580,7 @@
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
@@ -29499,7 +29611,7 @@
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
@@ -29530,7 +29642,7 @@
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -29561,7 +29673,7 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -29592,7 +29704,7 @@
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
@@ -29623,7 +29735,7 @@
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -29654,7 +29766,7 @@
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -29685,7 +29797,7 @@
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B564" s="2" t="inlineStr">
@@ -29716,7 +29828,7 @@
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -29747,7 +29859,7 @@
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -29778,7 +29890,7 @@
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B567" s="2" t="inlineStr">
@@ -29809,7 +29921,7 @@
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -29840,7 +29952,7 @@
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B569" s="2" t="inlineStr">
@@ -29871,7 +29983,7 @@
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B570" s="2" t="inlineStr">
@@ -29902,7 +30014,7 @@
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B571" s="2" t="inlineStr">
@@ -29933,7 +30045,7 @@
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B572" s="2" t="inlineStr">
@@ -29964,7 +30076,7 @@
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B573" s="2" t="inlineStr">
@@ -30003,7 +30115,7 @@
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B574" s="2" t="inlineStr">
@@ -30034,7 +30146,7 @@
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B575" s="2" t="inlineStr">
@@ -30073,7 +30185,7 @@
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B576" s="2" t="inlineStr">
@@ -30104,7 +30216,7 @@
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B577" s="2" t="inlineStr">
@@ -30135,7 +30247,7 @@
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B578" s="2" t="inlineStr">
@@ -30166,7 +30278,7 @@
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B579" s="2" t="inlineStr">
@@ -30197,7 +30309,7 @@
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B580" s="2" t="inlineStr">
@@ -30228,7 +30340,7 @@
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B581" s="2" t="inlineStr">
@@ -30256,8 +30368,644 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>Stored programme sums</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr"/>
+      <c r="F582" s="2" t="inlineStr"/>
+      <c r="G582" s="2" t="inlineStr"/>
+      <c r="H582" s="2" t="inlineStr"/>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>Stored strategy totals</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr"/>
+      <c r="F583" s="2" t="inlineStr"/>
+      <c r="G583" s="2" t="inlineStr"/>
+      <c r="H583" s="2" t="inlineStr"/>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>Programme counted once</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr"/>
+      <c r="F584" s="2" t="inlineStr"/>
+      <c r="G584" s="2" t="inlineStr"/>
+      <c r="H584" s="2" t="inlineStr"/>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>Ceiling holds</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr"/>
+      <c r="F585" s="2" t="inlineStr"/>
+      <c r="G585" s="2" t="inlineStr"/>
+      <c r="H585" s="2" t="inlineStr"/>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>Panel money matches its edges</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr"/>
+      <c r="F586" s="2" t="inlineStr"/>
+      <c r="G586" s="2" t="inlineStr"/>
+      <c r="H586" s="2" t="inlineStr"/>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>Edges cite real programmes</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr"/>
+      <c r="F587" s="2" t="inlineStr"/>
+      <c r="G587" s="2" t="inlineStr"/>
+      <c r="H587" s="2" t="inlineStr"/>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>No strategy dropped</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr"/>
+      <c r="H588" s="2" t="inlineStr"/>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>Unfunded list is complete</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr"/>
+      <c r="F589" s="2" t="inlineStr"/>
+      <c r="G589" s="2" t="inlineStr"/>
+      <c r="H589" s="2" t="inlineStr"/>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>Evidence chain resolves</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
+      <c r="F590" s="2" t="inlineStr"/>
+      <c r="G590" s="2" t="inlineStr"/>
+      <c r="H590" s="2" t="inlineStr"/>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>Maturity summary is derivable</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr"/>
+      <c r="F591" s="2" t="inlineStr"/>
+      <c r="G591" s="2" t="inlineStr"/>
+      <c r="H591" s="2" t="inlineStr"/>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>No duplicate edges</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr"/>
+      <c r="H592" s="2" t="inlineStr"/>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>One currency</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>1 expected</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr"/>
+      <c r="H593" s="2" t="inlineStr"/>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>Components are traceable</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
+      <c r="F594" s="2" t="inlineStr"/>
+      <c r="G594" s="2" t="inlineStr"/>
+      <c r="H594" s="2" t="inlineStr"/>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>No workbook open in Excel</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>0 expected</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr"/>
+      <c r="H595" s="2" t="inlineStr"/>
+      <c r="I595" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>Strategies come from the plan</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
+      <c r="F596" s="2" t="inlineStr"/>
+      <c r="G596" s="2" t="inlineStr"/>
+      <c r="H596" s="2" t="inlineStr"/>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>Funding priority is reproducible</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr"/>
+      <c r="F597" s="2" t="inlineStr"/>
+      <c r="G597" s="2" t="inlineStr"/>
+      <c r="H597" s="2" t="inlineStr"/>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>The budget is readable</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
+      <c r="F598" s="2" t="inlineStr"/>
+      <c r="G598" s="2" t="inlineStr"/>
+      <c r="H598" s="2" t="inlineStr"/>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous codes name their head</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr"/>
+      <c r="F599" s="2" t="inlineStr"/>
+      <c r="G599" s="2" t="inlineStr"/>
+      <c r="H599" s="2" t="inlineStr"/>
+      <c r="I599" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>Every intervention is traceable to a strategy</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
+      <c r="F600" s="2" t="inlineStr"/>
+      <c r="G600" s="2" t="inlineStr"/>
+      <c r="H600" s="2" t="inlineStr"/>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>The sector layer stayed out of the panel</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr"/>
+      <c r="F601" s="2" t="inlineStr"/>
+      <c r="G601" s="2" t="inlineStr"/>
+      <c r="H601" s="2" t="inlineStr"/>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I581"/>
+  <autoFilter ref="A1:I601"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30421,14 +31169,10 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>india;samoa;sri_lanka</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>stage 6 matched programme to strategy</t>
@@ -30444,7 +31188,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -30468,7 +31212,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>afghanistan;bhutan;brazil;brunei;china;fiji;ghana;jamaica;kenya;kiribati;malaysia;maldives;papua_new_guinea;thailand</t>
+          <t>afghanistan;bhutan;brazil;brunei;china;fiji;ghana;india;jamaica;kenya;kiribati;malaysia;maldives;papua_new_guinea;samoa;sri_lanka;thailand</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -30489,7 +31233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -30887,12 +31631,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -30902,12 +31646,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -30934,42 +31678,42 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -31258,324 +32002,324 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -31587,101 +32331,101 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -31711,24 +32455,24 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -31758,69 +32502,116 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>tuvalu</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>vanuatu</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DATA_AUDIT.xlsx
+++ b/DATA_AUDIT.xlsx
@@ -8132,24 +8132,16 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>PASS 2/4 - 2 FAIL</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>stage 5 missed programme rows the source contains</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
-        </is>
-      </c>
+          <t>PASS 4/4</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -27084,32 +27076,24 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>900 row(s)</t>
+          <t>367 row(s)</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>65 duplicate key(s)</t>
-        </is>
-      </c>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>calcs, funding_by_program</t>
-        </is>
-      </c>
-      <c r="H484" s="2" t="inlineStr">
-        <is>
-          <t>a programme-year counted twice is a union key collision: check budget_row_id suffixes in budget_rows.csv</t>
-        </is>
-      </c>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr"/>
+      <c r="H484" s="2" t="inlineStr"/>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>["FY2022 head 1 programme 1.1 appears 2 times", "FY2022 head 2 programme 2.2 appears 2 times", "FY2022 head 3 programme 3.3 appears 2 times", "FY2022 head 4 programme 4.4 appears 2 times", "FY2022 head 5 programme 5.5 appears 2 times", "FY2022 head 6 programme 6.6 appears 2 times", "FY2024 head 1 programme 1.1 appears 2 times", "FY2024 head 2 programme 2.2 appears 2 times"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27120,7 @@
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>165 strategy-year(s)</t>
+          <t>35 strategy-year(s)</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -32336,27 +32320,27 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -32371,7 +32355,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/DATA_AUDIT.xlsx
+++ b/DATA_AUDIT.xlsx
@@ -31196,7 +31196,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>afghanistan;bhutan;brazil;brunei;china;fiji;ghana;india;jamaica;kenya;kiribati;malaysia;maldives;papua_new_guinea;samoa;sri_lanka;thailand</t>
+          <t>afghanistan;bhutan;brazil;brunei;china;fiji;ghana;india;jamaica;kenya;kiribati;malaysia;maldives;papua_new_guinea;rwanda;samoa;sri_lanka</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">

--- a/DATA_AUDIT.xlsx
+++ b/DATA_AUDIT.xlsx
@@ -577,12 +577,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -590,16 +590,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -619,12 +611,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -632,16 +624,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -821,12 +805,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -834,16 +818,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -863,12 +839,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -876,16 +852,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1057,12 +1025,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1070,16 +1038,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1099,12 +1059,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1112,16 +1072,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1537,12 +1489,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1550,16 +1502,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1579,12 +1523,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1592,16 +1536,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1781,12 +1717,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1794,16 +1730,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1823,12 +1751,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1836,16 +1764,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2025,12 +1945,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2038,16 +1958,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2067,12 +1979,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2080,16 +1992,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3017,12 +2921,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -3030,16 +2934,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3059,12 +2955,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3072,16 +2968,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3269,12 +3157,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3282,16 +3170,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3311,12 +3191,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3324,16 +3204,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3521,12 +3393,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3534,16 +3406,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3563,12 +3427,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3576,16 +3440,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4001,12 +3857,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4014,16 +3870,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4043,12 +3891,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4056,16 +3904,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4245,12 +4085,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4258,16 +4098,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4287,12 +4119,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4300,16 +4132,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4741,12 +4565,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -4754,16 +4578,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4783,12 +4599,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -4796,16 +4612,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4993,12 +4801,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5006,16 +4814,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5035,12 +4835,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -5048,16 +4848,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5481,12 +5273,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -5494,16 +5286,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5523,12 +5307,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -5536,16 +5320,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5733,12 +5509,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -5746,16 +5522,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5775,12 +5543,12 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -5788,16 +5556,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5969,12 +5729,12 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -5982,16 +5742,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6011,12 +5763,12 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -6024,16 +5776,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -6929,12 +6673,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -6942,16 +6686,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6971,12 +6707,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -6984,16 +6720,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -7173,12 +6901,12 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -7186,16 +6914,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -7215,12 +6935,12 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -7228,16 +6948,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -7661,12 +7373,12 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -7674,16 +7386,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -7703,12 +7407,12 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -7716,16 +7420,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -7897,12 +7593,12 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -7910,16 +7606,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -7939,12 +7627,12 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -7952,16 +7640,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -8149,12 +7829,12 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -8162,16 +7842,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -8191,12 +7863,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -8204,16 +7876,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -8637,12 +8301,12 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -8650,16 +8314,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -8679,12 +8335,12 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -8692,16 +8348,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -8881,12 +8529,12 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -8894,16 +8542,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -8923,12 +8563,12 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -8936,16 +8576,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H209" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -9125,12 +8757,12 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -9138,16 +8770,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -9167,12 +8791,12 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -9180,16 +8804,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -9621,12 +9237,12 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -9634,16 +9250,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -9663,12 +9271,12 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
@@ -9676,16 +9284,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -9857,12 +9457,12 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -9870,16 +9470,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -9899,12 +9491,12 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -9912,16 +9504,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H233" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -10541,12 +10125,12 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
@@ -10554,16 +10138,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -10583,12 +10159,12 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -10596,16 +10172,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -10777,12 +10345,12 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -10790,16 +10358,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -10819,12 +10379,12 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
@@ -10832,16 +10392,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -11021,12 +10573,12 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -11034,16 +10586,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H262" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -11063,12 +10607,12 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
@@ -11076,16 +10620,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -11509,12 +11045,12 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -11522,16 +11058,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H274" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -11551,12 +11079,12 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -11564,16 +11092,8 @@
           <t>NOT CONFIGURED - this figure was never checked against the source</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
-        <is>
-          <t>no source document is named for this check to read</t>
-        </is>
-      </c>
-      <c r="H275" s="2" t="inlineStr">
-        <is>
-          <t>add check_against.fidelity_sources / grand_totals / evidence_sources to configs/&lt;slug&gt;.json and re-run pv2.run</t>
-        </is>
-      </c>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">

--- a/DATA_AUDIT.xlsx
+++ b/DATA_AUDIT.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'validators'!$A$1:$H$283</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'self-audit'!$A$1:$I$621</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'self-audit'!$A$1:$I$641</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'funnel'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'basis'!$A$1:$I$30</definedName>
   </definedNames>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/2 - 2 input(s) not on this machine</t>
+          <t>PASS 1/1</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
@@ -5920,16 +5920,24 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 input(s) not on this machine</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -11427,7 +11435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I621"/>
+  <dimension ref="A1:I641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23195,7 +23203,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -23210,19 +23218,11 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F322" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr"/>
+      <c r="F322" s="2" t="inlineStr"/>
       <c r="G322" s="2" t="inlineStr"/>
       <c r="H322" s="2" t="inlineStr"/>
       <c r="I322" s="2" t="inlineStr">
@@ -23234,7 +23234,7 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -23249,19 +23249,11 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr"/>
+      <c r="F323" s="2" t="inlineStr"/>
       <c r="G323" s="2" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr"/>
       <c r="I323" s="2" t="inlineStr">
@@ -23273,7 +23265,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -23304,7 +23296,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -23319,19 +23311,11 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F325" s="2" t="inlineStr">
-        <is>
-          <t>0 over ceiling</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr"/>
+      <c r="F325" s="2" t="inlineStr"/>
       <c r="G325" s="2" t="inlineStr"/>
       <c r="H325" s="2" t="inlineStr"/>
       <c r="I325" s="2" t="inlineStr">
@@ -23343,7 +23327,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -23374,7 +23358,7 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -23405,7 +23389,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -23425,12 +23409,12 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>17 strategyclean row(s)</t>
+          <t>260 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>17 panel row(s)</t>
+          <t>260 panel row(s)</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr"/>
@@ -23444,7 +23428,7 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -23475,7 +23459,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -23490,31 +23474,39 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>45 distinct id(s)</t>
+          <t>668 distinct id(s)</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>0 dangle</t>
-        </is>
-      </c>
-      <c r="G330" s="2" t="inlineStr"/>
-      <c r="H330" s="2" t="inlineStr"/>
+          <t>2 dangle</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>stage 3 to 4, the evidence chain</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>a source_chunks id resolves to no stage-3 row: re-run stage 4 (consolidation) against the current strategy_rows</t>
+        </is>
+      </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["chunk id 0 has no stage-3 row", "chunk id 1 has no stage-3 row"]</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -23553,7 +23545,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -23584,7 +23576,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -23609,7 +23601,7 @@
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
+          <t>0 found</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr"/>
@@ -23623,7 +23615,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -23662,7 +23654,7 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -23701,7 +23693,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -23721,7 +23713,7 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>17 strategy(ies)</t>
+          <t>260 strategy(ies)</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
@@ -23740,7 +23732,7 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -23771,7 +23763,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -23802,7 +23794,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -23833,7 +23825,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -23853,7 +23845,7 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>45 intervention(s) extracted</t>
+          <t>666 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
@@ -23872,7 +23864,7 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>nauru</t>
+          <t>mongolia</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -23903,7 +23895,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -23918,11 +23910,19 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="inlineStr"/>
-      <c r="F342" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>50 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G342" s="2" t="inlineStr"/>
       <c r="H342" s="2" t="inlineStr"/>
       <c r="I342" s="2" t="inlineStr">
@@ -23934,7 +23934,7 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -23949,11 +23949,19 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E343" s="2" t="inlineStr"/>
-      <c r="F343" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>50 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G343" s="2" t="inlineStr"/>
       <c r="H343" s="2" t="inlineStr"/>
       <c r="I343" s="2" t="inlineStr">
@@ -23965,7 +23973,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -23980,19 +23988,11 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E344" s="2" t="inlineStr">
-        <is>
-          <t>482 row(s)</t>
-        </is>
-      </c>
-      <c r="F344" s="2" t="inlineStr">
-        <is>
-          <t>0 duplicate key(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr"/>
+      <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr"/>
       <c r="H344" s="2" t="inlineStr"/>
       <c r="I344" s="2" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>91 strategy-year(s)</t>
+          <t>50 strategy-year(s)</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr">
@@ -24043,7 +24043,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -24074,7 +24074,7 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -24105,7 +24105,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -24120,11 +24120,19 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E348" s="2" t="inlineStr"/>
-      <c r="F348" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>17 strategyclean row(s)</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>17 panel row(s)</t>
+        </is>
+      </c>
       <c r="G348" s="2" t="inlineStr"/>
       <c r="H348" s="2" t="inlineStr"/>
       <c r="I348" s="2" t="inlineStr">
@@ -24136,7 +24144,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -24167,7 +24175,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -24182,11 +24190,19 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E350" s="2" t="inlineStr"/>
-      <c r="F350" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>45 distinct id(s)</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>0 dangle</t>
+        </is>
+      </c>
       <c r="G350" s="2" t="inlineStr"/>
       <c r="H350" s="2" t="inlineStr"/>
       <c r="I350" s="2" t="inlineStr">
@@ -24198,7 +24214,7 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -24213,11 +24229,19 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E351" s="2" t="inlineStr"/>
-      <c r="F351" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>1 metric(s)</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G351" s="2" t="inlineStr"/>
       <c r="H351" s="2" t="inlineStr"/>
       <c r="I351" s="2" t="inlineStr">
@@ -24229,7 +24253,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -24260,7 +24284,7 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -24285,7 +24309,7 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>0 found</t>
+          <t>1 found</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr"/>
@@ -24299,7 +24323,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -24314,11 +24338,19 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr"/>
-      <c r="F354" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>0 component(s)</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>0 untraceable</t>
+        </is>
+      </c>
       <c r="G354" s="2" t="inlineStr"/>
       <c r="H354" s="2" t="inlineStr"/>
       <c r="I354" s="2" t="inlineStr">
@@ -24330,7 +24362,7 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -24369,7 +24401,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -24384,11 +24416,19 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E356" s="2" t="inlineStr"/>
-      <c r="F356" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>17 strategy(ies)</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>0 with no component</t>
+        </is>
+      </c>
       <c r="G356" s="2" t="inlineStr"/>
       <c r="H356" s="2" t="inlineStr"/>
       <c r="I356" s="2" t="inlineStr">
@@ -24400,7 +24440,7 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -24431,7 +24471,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -24462,7 +24502,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -24493,7 +24533,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -24508,11 +24548,19 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr"/>
-      <c r="F360" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>45 intervention(s) extracted</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>0 uncited (0.0%)</t>
+        </is>
+      </c>
       <c r="G360" s="2" t="inlineStr"/>
       <c r="H360" s="2" t="inlineStr"/>
       <c r="I360" s="2" t="inlineStr">
@@ -24524,7 +24572,7 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>nepal</t>
+          <t>nauru</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -24555,7 +24603,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -24586,7 +24634,7 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -24617,7 +24665,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -24632,11 +24680,19 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E364" s="2" t="inlineStr"/>
-      <c r="F364" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>482 row(s)</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
       <c r="G364" s="2" t="inlineStr"/>
       <c r="H364" s="2" t="inlineStr"/>
       <c r="I364" s="2" t="inlineStr">
@@ -24648,7 +24704,7 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -24663,11 +24719,19 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="inlineStr"/>
-      <c r="F365" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>91 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>0 over ceiling</t>
+        </is>
+      </c>
       <c r="G365" s="2" t="inlineStr"/>
       <c r="H365" s="2" t="inlineStr"/>
       <c r="I365" s="2" t="inlineStr">
@@ -24679,7 +24743,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -24710,7 +24774,7 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -24741,7 +24805,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -24772,7 +24836,7 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -24803,7 +24867,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -24834,7 +24898,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -24865,7 +24929,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -24896,7 +24960,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -24935,7 +24999,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -24966,7 +25030,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -25005,7 +25069,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -25036,7 +25100,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -25067,7 +25131,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -25098,7 +25162,7 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -25129,7 +25193,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -25160,7 +25224,7 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>nigeria</t>
+          <t>nepal</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -25191,7 +25255,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -25222,7 +25286,7 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -25253,7 +25317,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -25284,7 +25348,7 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -25315,7 +25379,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -25346,7 +25410,7 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -25377,7 +25441,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -25408,7 +25472,7 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -25439,7 +25503,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -25470,7 +25534,7 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -25501,7 +25565,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -25532,7 +25596,7 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -25571,7 +25635,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -25602,7 +25666,7 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -25641,7 +25705,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -25672,7 +25736,7 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -25703,7 +25767,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -25734,7 +25798,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -25765,7 +25829,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -25796,7 +25860,7 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>pakistan</t>
+          <t>nigeria</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -25827,7 +25891,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -25842,19 +25906,11 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E402" s="2" t="inlineStr">
-        <is>
-          <t>22 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F402" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr"/>
+      <c r="F402" s="2" t="inlineStr"/>
       <c r="G402" s="2" t="inlineStr"/>
       <c r="H402" s="2" t="inlineStr"/>
       <c r="I402" s="2" t="inlineStr">
@@ -25866,7 +25922,7 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -25881,19 +25937,11 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E403" s="2" t="inlineStr">
-        <is>
-          <t>22 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F403" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr"/>
+      <c r="F403" s="2" t="inlineStr"/>
       <c r="G403" s="2" t="inlineStr"/>
       <c r="H403" s="2" t="inlineStr"/>
       <c r="I403" s="2" t="inlineStr">
@@ -25905,7 +25953,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -25920,19 +25968,11 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E404" s="2" t="inlineStr">
-        <is>
-          <t>159 row(s)</t>
-        </is>
-      </c>
-      <c r="F404" s="2" t="inlineStr">
-        <is>
-          <t>0 duplicate key(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr"/>
+      <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr"/>
       <c r="H404" s="2" t="inlineStr"/>
       <c r="I404" s="2" t="inlineStr">
@@ -25944,7 +25984,7 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -25959,19 +25999,11 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E405" s="2" t="inlineStr">
-        <is>
-          <t>104 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F405" s="2" t="inlineStr">
-        <is>
-          <t>0 over ceiling</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr"/>
+      <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr"/>
       <c r="H405" s="2" t="inlineStr"/>
       <c r="I405" s="2" t="inlineStr">
@@ -25983,7 +26015,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -25998,19 +26030,11 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E406" s="2" t="inlineStr">
-        <is>
-          <t>89 strategy-year figure(s)</t>
-        </is>
-      </c>
-      <c r="F406" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr"/>
+      <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr"/>
       <c r="H406" s="2" t="inlineStr"/>
       <c r="I406" s="2" t="inlineStr">
@@ -26022,7 +26046,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -26053,7 +26077,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -26068,19 +26092,11 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E408" s="2" t="inlineStr">
-        <is>
-          <t>89 strategyclean row(s)</t>
-        </is>
-      </c>
-      <c r="F408" s="2" t="inlineStr">
-        <is>
-          <t>89 panel row(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr"/>
+      <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr"/>
       <c r="H408" s="2" t="inlineStr"/>
       <c r="I408" s="2" t="inlineStr">
@@ -26092,7 +26108,7 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -26123,7 +26139,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -26138,19 +26154,11 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E410" s="2" t="inlineStr">
-        <is>
-          <t>855 distinct id(s)</t>
-        </is>
-      </c>
-      <c r="F410" s="2" t="inlineStr">
-        <is>
-          <t>0 dangle</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr"/>
+      <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr"/>
       <c r="H410" s="2" t="inlineStr"/>
       <c r="I410" s="2" t="inlineStr">
@@ -26162,7 +26170,7 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -26177,19 +26185,11 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E411" s="2" t="inlineStr">
-        <is>
-          <t>1 metric(s)</t>
-        </is>
-      </c>
-      <c r="F411" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr"/>
+      <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr"/>
       <c r="H411" s="2" t="inlineStr"/>
       <c r="I411" s="2" t="inlineStr">
@@ -26201,7 +26201,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -26232,7 +26232,7 @@
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
+          <t>0 found</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr"/>
@@ -26271,7 +26271,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -26286,19 +26286,11 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E414" s="2" t="inlineStr">
-        <is>
-          <t>0 component(s)</t>
-        </is>
-      </c>
-      <c r="F414" s="2" t="inlineStr">
-        <is>
-          <t>0 untraceable</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr"/>
+      <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr"/>
       <c r="H414" s="2" t="inlineStr"/>
       <c r="I414" s="2" t="inlineStr">
@@ -26310,7 +26302,7 @@
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -26349,7 +26341,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -26364,19 +26356,11 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E416" s="2" t="inlineStr">
-        <is>
-          <t>89 strategy(ies)</t>
-        </is>
-      </c>
-      <c r="F416" s="2" t="inlineStr">
-        <is>
-          <t>0 with no component</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr"/>
+      <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr"/>
       <c r="H416" s="2" t="inlineStr"/>
       <c r="I416" s="2" t="inlineStr">
@@ -26388,7 +26372,7 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -26419,7 +26403,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -26434,19 +26418,11 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E418" s="2" t="inlineStr">
-        <is>
-          <t>48 programme(s)</t>
-        </is>
-      </c>
-      <c r="F418" s="2" t="inlineStr">
-        <is>
-          <t>0 unreadable (0%), carrying 0% of the money</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr"/>
+      <c r="F418" s="2" t="inlineStr"/>
       <c r="G418" s="2" t="inlineStr"/>
       <c r="H418" s="2" t="inlineStr"/>
       <c r="I418" s="2" t="inlineStr">
@@ -26458,7 +26434,7 @@
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -26489,7 +26465,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -26504,31 +26480,23 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E420" s="2" t="inlineStr">
-        <is>
-          <t>867 intervention(s) extracted</t>
-        </is>
-      </c>
-      <c r="F420" s="2" t="inlineStr">
-        <is>
-          <t>12 uncited (1.4%)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr"/>
+      <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr"/>
       <c r="H420" s="2" t="inlineStr"/>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>["207", "210", "272", "314", "421", "422", "431", "434"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>papua_new_guinea</t>
+          <t>pakistan</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -26559,7 +26527,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -26579,7 +26547,7 @@
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>22 strategy-year(s)</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
@@ -26598,7 +26566,7 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -26618,7 +26586,7 @@
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>22 strategy-year(s)</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -26637,7 +26605,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -26657,7 +26625,7 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>74 row(s)</t>
+          <t>159 row(s)</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
@@ -26676,7 +26644,7 @@
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -26696,7 +26664,7 @@
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>104 strategy-year(s)</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
@@ -26715,7 +26683,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -26735,7 +26703,7 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>106 strategy-year figure(s)</t>
+          <t>89 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
@@ -26754,7 +26722,7 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -26785,7 +26753,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -26805,12 +26773,12 @@
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>106 strategyclean row(s)</t>
+          <t>89 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>106 panel row(s)</t>
+          <t>89 panel row(s)</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr"/>
@@ -26824,7 +26792,7 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -26855,7 +26823,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -26875,7 +26843,7 @@
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>617 distinct id(s)</t>
+          <t>855 distinct id(s)</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
@@ -26894,7 +26862,7 @@
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -26933,7 +26901,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -26964,7 +26932,7 @@
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -27003,7 +26971,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -27042,7 +27010,7 @@
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -27081,7 +27049,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -27101,7 +27069,7 @@
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>106 strategy(ies)</t>
+          <t>89 strategy(ies)</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
@@ -27120,7 +27088,7 @@
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -27151,7 +27119,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -27171,7 +27139,7 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>74 programme(s)</t>
+          <t>48 programme(s)</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
@@ -27190,7 +27158,7 @@
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -27221,7 +27189,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -27241,26 +27209,26 @@
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>617 intervention(s) extracted</t>
+          <t>867 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>0 uncited (0.0%)</t>
+          <t>12 uncited (1.4%)</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="2" t="inlineStr"/>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["207", "210", "272", "314", "421", "422", "431", "434"]</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>rwanda</t>
+          <t>papua_new_guinea</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -27291,7 +27259,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -27311,7 +27279,7 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>83 strategy-year(s)</t>
+          <t>11 strategy-year(s)</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
@@ -27330,7 +27298,7 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -27350,7 +27318,7 @@
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>83 strategy-year(s)</t>
+          <t>11 strategy-year(s)</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
@@ -27369,7 +27337,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -27389,7 +27357,7 @@
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>143 row(s)</t>
+          <t>74 row(s)</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
@@ -27408,7 +27376,7 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -27428,7 +27396,7 @@
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>36 strategy-year(s)</t>
+          <t>11 strategy-year(s)</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
@@ -27447,7 +27415,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -27467,7 +27435,7 @@
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year figure(s)</t>
+          <t>106 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr">
@@ -27486,7 +27454,7 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -27517,7 +27485,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -27537,12 +27505,12 @@
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>28 strategyclean row(s)</t>
+          <t>106 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>28 panel row(s)</t>
+          <t>106 panel row(s)</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr"/>
@@ -27556,7 +27524,7 @@
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -27587,7 +27555,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -27607,7 +27575,7 @@
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>140 distinct id(s)</t>
+          <t>617 distinct id(s)</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -27626,7 +27594,7 @@
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -27665,7 +27633,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -27696,7 +27664,7 @@
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -27735,7 +27703,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -27774,7 +27742,7 @@
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -27813,7 +27781,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -27833,7 +27801,7 @@
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>28 strategy(ies)</t>
+          <t>106 strategy(ies)</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr">
@@ -27852,7 +27820,7 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -27883,7 +27851,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -27903,7 +27871,7 @@
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>191 programme(s)</t>
+          <t>74 programme(s)</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -27922,7 +27890,7 @@
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -27953,7 +27921,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
@@ -27973,7 +27941,7 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>140 intervention(s) extracted</t>
+          <t>617 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -27992,7 +27960,7 @@
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>samoa</t>
+          <t>rwanda</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -28023,7 +27991,7 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -28038,11 +28006,19 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E462" s="2" t="inlineStr"/>
-      <c r="F462" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>83 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G462" s="2" t="inlineStr"/>
       <c r="H462" s="2" t="inlineStr"/>
       <c r="I462" s="2" t="inlineStr">
@@ -28054,7 +28030,7 @@
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -28069,11 +28045,19 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E463" s="2" t="inlineStr"/>
-      <c r="F463" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>83 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr"/>
       <c r="I463" s="2" t="inlineStr">
@@ -28085,7 +28069,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -28105,7 +28089,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>83 row(s)</t>
+          <t>143 row(s)</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -28124,7 +28108,7 @@
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -28144,7 +28128,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>8 strategy-year(s)</t>
+          <t>36 strategy-year(s)</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -28163,7 +28147,7 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -28178,11 +28162,19 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E466" s="2" t="inlineStr"/>
-      <c r="F466" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>28 strategy-year figure(s)</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G466" s="2" t="inlineStr"/>
       <c r="H466" s="2" t="inlineStr"/>
       <c r="I466" s="2" t="inlineStr">
@@ -28194,7 +28186,7 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -28225,7 +28217,7 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -28240,11 +28232,19 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E468" s="2" t="inlineStr"/>
-      <c r="F468" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>28 strategyclean row(s)</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>28 panel row(s)</t>
+        </is>
+      </c>
       <c r="G468" s="2" t="inlineStr"/>
       <c r="H468" s="2" t="inlineStr"/>
       <c r="I468" s="2" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -28287,7 +28287,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -28302,11 +28302,19 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="inlineStr"/>
-      <c r="F470" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>140 distinct id(s)</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>0 dangle</t>
+        </is>
+      </c>
       <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr"/>
       <c r="I470" s="2" t="inlineStr">
@@ -28318,7 +28326,7 @@
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -28333,11 +28341,19 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E471" s="2" t="inlineStr"/>
-      <c r="F471" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>1 metric(s)</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G471" s="2" t="inlineStr"/>
       <c r="H471" s="2" t="inlineStr"/>
       <c r="I471" s="2" t="inlineStr">
@@ -28349,7 +28365,7 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -28380,7 +28396,7 @@
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -28405,7 +28421,7 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>0 found</t>
+          <t>1 found</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr"/>
@@ -28419,7 +28435,7 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -28434,11 +28450,19 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E474" s="2" t="inlineStr"/>
-      <c r="F474" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>0 component(s)</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>0 untraceable</t>
+        </is>
+      </c>
       <c r="G474" s="2" t="inlineStr"/>
       <c r="H474" s="2" t="inlineStr"/>
       <c r="I474" s="2" t="inlineStr">
@@ -28450,7 +28474,7 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -28489,7 +28513,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -28504,11 +28528,19 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E476" s="2" t="inlineStr"/>
-      <c r="F476" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>28 strategy(ies)</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>0 with no component</t>
+        </is>
+      </c>
       <c r="G476" s="2" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr"/>
       <c r="I476" s="2" t="inlineStr">
@@ -28520,7 +28552,7 @@
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -28551,7 +28583,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -28566,11 +28598,19 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E478" s="2" t="inlineStr"/>
-      <c r="F478" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>191 programme(s)</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>0 unreadable (0%), carrying 0% of the money</t>
+        </is>
+      </c>
       <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr"/>
       <c r="I478" s="2" t="inlineStr">
@@ -28582,7 +28622,7 @@
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -28613,7 +28653,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -28628,11 +28668,19 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E480" s="2" t="inlineStr"/>
-      <c r="F480" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>140 intervention(s) extracted</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>0 uncited (0.0%)</t>
+        </is>
+      </c>
       <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr"/>
       <c r="I480" s="2" t="inlineStr">
@@ -28644,7 +28692,7 @@
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>solomon_islands</t>
+          <t>samoa</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -28675,7 +28723,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -28690,19 +28738,11 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E482" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F482" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr"/>
+      <c r="F482" s="2" t="inlineStr"/>
       <c r="G482" s="2" t="inlineStr"/>
       <c r="H482" s="2" t="inlineStr"/>
       <c r="I482" s="2" t="inlineStr">
@@ -28714,7 +28754,7 @@
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -28729,19 +28769,11 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E483" s="2" t="inlineStr">
-        <is>
-          <t>50 strategy-year(s)</t>
-        </is>
-      </c>
-      <c r="F483" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr"/>
+      <c r="F483" s="2" t="inlineStr"/>
       <c r="G483" s="2" t="inlineStr"/>
       <c r="H483" s="2" t="inlineStr"/>
       <c r="I483" s="2" t="inlineStr">
@@ -28753,7 +28785,7 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -28773,7 +28805,7 @@
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>140 row(s)</t>
+          <t>83 row(s)</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr">
@@ -28792,7 +28824,7 @@
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -28812,7 +28844,7 @@
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>6 strategy-year(s)</t>
+          <t>8 strategy-year(s)</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -28831,7 +28863,7 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -28846,19 +28878,11 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E486" s="2" t="inlineStr">
-        <is>
-          <t>143 strategy-year figure(s)</t>
-        </is>
-      </c>
-      <c r="F486" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr"/>
+      <c r="F486" s="2" t="inlineStr"/>
       <c r="G486" s="2" t="inlineStr"/>
       <c r="H486" s="2" t="inlineStr"/>
       <c r="I486" s="2" t="inlineStr">
@@ -28870,7 +28894,7 @@
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -28901,7 +28925,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -28916,19 +28940,11 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E488" s="2" t="inlineStr">
-        <is>
-          <t>143 strategyclean row(s)</t>
-        </is>
-      </c>
-      <c r="F488" s="2" t="inlineStr">
-        <is>
-          <t>143 panel row(s)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr"/>
+      <c r="F488" s="2" t="inlineStr"/>
       <c r="G488" s="2" t="inlineStr"/>
       <c r="H488" s="2" t="inlineStr"/>
       <c r="I488" s="2" t="inlineStr">
@@ -28940,7 +28956,7 @@
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -28971,7 +28987,7 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -28986,19 +29002,11 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr">
-        <is>
-          <t>957 distinct id(s)</t>
-        </is>
-      </c>
-      <c r="F490" s="2" t="inlineStr">
-        <is>
-          <t>0 dangle</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr"/>
+      <c r="F490" s="2" t="inlineStr"/>
       <c r="G490" s="2" t="inlineStr"/>
       <c r="H490" s="2" t="inlineStr"/>
       <c r="I490" s="2" t="inlineStr">
@@ -29010,7 +29018,7 @@
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -29025,19 +29033,11 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E491" s="2" t="inlineStr">
-        <is>
-          <t>1 metric(s)</t>
-        </is>
-      </c>
-      <c r="F491" s="2" t="inlineStr">
-        <is>
-          <t>0 disagree</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr"/>
+      <c r="F491" s="2" t="inlineStr"/>
       <c r="G491" s="2" t="inlineStr"/>
       <c r="H491" s="2" t="inlineStr"/>
       <c r="I491" s="2" t="inlineStr">
@@ -29049,7 +29049,7 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -29080,7 +29080,7 @@
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -29095,7 +29095,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -29105,29 +29105,21 @@
       </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>2 found</t>
-        </is>
-      </c>
-      <c r="G493" s="2" t="inlineStr">
-        <is>
-          <t>the config, currency_unit</t>
-        </is>
-      </c>
-      <c r="H493" s="2" t="inlineStr">
-        <is>
-          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
-        </is>
-      </c>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr"/>
+      <c r="H493" s="2" t="inlineStr"/>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>["Rs. Billion", "Rs.Mn"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -29142,19 +29134,11 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>0 component(s)</t>
-        </is>
-      </c>
-      <c r="F494" s="2" t="inlineStr">
-        <is>
-          <t>0 untraceable</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr"/>
+      <c r="F494" s="2" t="inlineStr"/>
       <c r="G494" s="2" t="inlineStr"/>
       <c r="H494" s="2" t="inlineStr"/>
       <c r="I494" s="2" t="inlineStr">
@@ -29166,7 +29150,7 @@
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -29205,7 +29189,7 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -29220,19 +29204,11 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>143 strategy(ies)</t>
-        </is>
-      </c>
-      <c r="F496" s="2" t="inlineStr">
-        <is>
-          <t>0 with no component</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr"/>
+      <c r="F496" s="2" t="inlineStr"/>
       <c r="G496" s="2" t="inlineStr"/>
       <c r="H496" s="2" t="inlineStr"/>
       <c r="I496" s="2" t="inlineStr">
@@ -29244,7 +29220,7 @@
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -29275,7 +29251,7 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -29306,7 +29282,7 @@
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -29337,7 +29313,7 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -29352,31 +29328,23 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E500" s="2" t="inlineStr">
-        <is>
-          <t>958 intervention(s) extracted</t>
-        </is>
-      </c>
-      <c r="F500" s="2" t="inlineStr">
-        <is>
-          <t>1 uncited (0.1%)</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr"/>
+      <c r="F500" s="2" t="inlineStr"/>
       <c r="G500" s="2" t="inlineStr"/>
       <c r="H500" s="2" t="inlineStr"/>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>["2205"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>sri_lanka</t>
+          <t>solomon_islands</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -29407,7 +29375,7 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -29427,7 +29395,7 @@
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year(s)</t>
+          <t>50 strategy-year(s)</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -29446,7 +29414,7 @@
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -29466,7 +29434,7 @@
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year(s)</t>
+          <t>50 strategy-year(s)</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
@@ -29485,7 +29453,7 @@
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -29505,7 +29473,7 @@
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>367 row(s)</t>
+          <t>140 row(s)</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -29524,7 +29492,7 @@
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -29544,7 +29512,7 @@
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>35 strategy-year(s)</t>
+          <t>6 strategy-year(s)</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr">
@@ -29563,7 +29531,7 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -29583,7 +29551,7 @@
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>99 strategy-year figure(s)</t>
+          <t>143 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr">
@@ -29602,7 +29570,7 @@
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -29633,7 +29601,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -29653,12 +29621,12 @@
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>99 strategyclean row(s)</t>
+          <t>143 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>99 panel row(s)</t>
+          <t>143 panel row(s)</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr"/>
@@ -29672,7 +29640,7 @@
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -29703,7 +29671,7 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
@@ -29723,7 +29691,7 @@
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>525 distinct id(s)</t>
+          <t>957 distinct id(s)</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr">
@@ -29742,7 +29710,7 @@
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
@@ -29781,7 +29749,7 @@
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
@@ -29812,7 +29780,7 @@
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
@@ -29827,7 +29795,7 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -29837,21 +29805,29 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
-        </is>
-      </c>
-      <c r="G513" s="2" t="inlineStr"/>
-      <c r="H513" s="2" t="inlineStr"/>
+          <t>2 found</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>the config, currency_unit</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
+        </is>
+      </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Rs. Billion", "Rs.Mn"]</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
@@ -29890,7 +29866,7 @@
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
@@ -29929,7 +29905,7 @@
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
@@ -29949,7 +29925,7 @@
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>99 strategy(ies)</t>
+          <t>143 strategy(ies)</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
@@ -29968,7 +29944,7 @@
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
@@ -29999,7 +29975,7 @@
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
@@ -30014,19 +29990,11 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr">
-        <is>
-          <t>273 programme(s)</t>
-        </is>
-      </c>
-      <c r="F518" s="2" t="inlineStr">
-        <is>
-          <t>0 unreadable (0%), carrying 0% of the money</t>
-        </is>
-      </c>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr"/>
+      <c r="F518" s="2" t="inlineStr"/>
       <c r="G518" s="2" t="inlineStr"/>
       <c r="H518" s="2" t="inlineStr"/>
       <c r="I518" s="2" t="inlineStr">
@@ -30038,7 +30006,7 @@
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
@@ -30069,7 +30037,7 @@
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
@@ -30089,26 +30057,26 @@
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>533 intervention(s) extracted</t>
+          <t>958 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>8 uncited (1.5%)</t>
+          <t>1 uncited (0.1%)</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr"/>
       <c r="H520" s="2" t="inlineStr"/>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>["202", "369", "383", "452", "472", "497", "503", "771"]</t>
+          <t>["2205"]</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>thailand</t>
+          <t>sri_lanka</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
@@ -30139,7 +30107,7 @@
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
@@ -30159,7 +30127,7 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>2 strategy-year(s)</t>
+          <t>28 strategy-year(s)</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -30178,7 +30146,7 @@
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -30198,7 +30166,7 @@
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>2 strategy-year(s)</t>
+          <t>28 strategy-year(s)</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -30217,7 +30185,7 @@
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
@@ -30237,7 +30205,7 @@
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>17 row(s)</t>
+          <t>367 row(s)</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr">
@@ -30256,7 +30224,7 @@
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -30276,7 +30244,7 @@
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>2 strategy-year(s)</t>
+          <t>35 strategy-year(s)</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
@@ -30295,7 +30263,7 @@
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
@@ -30315,7 +30283,7 @@
       </c>
       <c r="E526" s="2" t="inlineStr">
         <is>
-          <t>6 strategy-year figure(s)</t>
+          <t>99 strategy-year figure(s)</t>
         </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
@@ -30334,7 +30302,7 @@
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B527" s="2" t="inlineStr">
@@ -30365,7 +30333,7 @@
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B528" s="2" t="inlineStr">
@@ -30385,12 +30353,12 @@
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>6 strategyclean row(s)</t>
+          <t>99 strategyclean row(s)</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>6 panel row(s)</t>
+          <t>99 panel row(s)</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr"/>
@@ -30404,7 +30372,7 @@
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B529" s="2" t="inlineStr">
@@ -30435,7 +30403,7 @@
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
@@ -30455,7 +30423,7 @@
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>4 distinct id(s)</t>
+          <t>525 distinct id(s)</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
@@ -30474,7 +30442,7 @@
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
@@ -30513,7 +30481,7 @@
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
@@ -30544,7 +30512,7 @@
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -30583,7 +30551,7 @@
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
@@ -30622,7 +30590,7 @@
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
@@ -30661,7 +30629,7 @@
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
@@ -30681,7 +30649,7 @@
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>6 strategy(ies)</t>
+          <t>99 strategy(ies)</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
@@ -30700,7 +30668,7 @@
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
@@ -30731,7 +30699,7 @@
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
@@ -30751,7 +30719,7 @@
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>17 programme(s)</t>
+          <t>273 programme(s)</t>
         </is>
       </c>
       <c r="F538" s="2" t="inlineStr">
@@ -30770,7 +30738,7 @@
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
@@ -30801,7 +30769,7 @@
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
@@ -30821,26 +30789,26 @@
       </c>
       <c r="E540" s="2" t="inlineStr">
         <is>
-          <t>4 intervention(s) extracted</t>
+          <t>533 intervention(s) extracted</t>
         </is>
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>0 uncited (0.0%)</t>
+          <t>8 uncited (1.5%)</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr"/>
       <c r="H540" s="2" t="inlineStr"/>
       <c r="I540" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["202", "369", "383", "452", "472", "497", "503", "771"]</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>thailand_test</t>
+          <t>thailand</t>
         </is>
       </c>
       <c r="B541" s="2" t="inlineStr">
@@ -30871,7 +30839,7 @@
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B542" s="2" t="inlineStr">
@@ -30886,11 +30854,19 @@
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E542" s="2" t="inlineStr"/>
-      <c r="F542" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>2 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G542" s="2" t="inlineStr"/>
       <c r="H542" s="2" t="inlineStr"/>
       <c r="I542" s="2" t="inlineStr">
@@ -30902,7 +30878,7 @@
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B543" s="2" t="inlineStr">
@@ -30917,11 +30893,19 @@
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E543" s="2" t="inlineStr"/>
-      <c r="F543" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>2 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G543" s="2" t="inlineStr"/>
       <c r="H543" s="2" t="inlineStr"/>
       <c r="I543" s="2" t="inlineStr">
@@ -30933,7 +30917,7 @@
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
@@ -30948,11 +30932,19 @@
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E544" s="2" t="inlineStr"/>
-      <c r="F544" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>17 row(s)</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>0 duplicate key(s)</t>
+        </is>
+      </c>
       <c r="G544" s="2" t="inlineStr"/>
       <c r="H544" s="2" t="inlineStr"/>
       <c r="I544" s="2" t="inlineStr">
@@ -30964,7 +30956,7 @@
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
@@ -30979,11 +30971,19 @@
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E545" s="2" t="inlineStr"/>
-      <c r="F545" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>2 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>0 over ceiling</t>
+        </is>
+      </c>
       <c r="G545" s="2" t="inlineStr"/>
       <c r="H545" s="2" t="inlineStr"/>
       <c r="I545" s="2" t="inlineStr">
@@ -30995,7 +30995,7 @@
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
@@ -31010,11 +31010,19 @@
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E546" s="2" t="inlineStr"/>
-      <c r="F546" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>6 strategy-year figure(s)</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G546" s="2" t="inlineStr"/>
       <c r="H546" s="2" t="inlineStr"/>
       <c r="I546" s="2" t="inlineStr">
@@ -31026,7 +31034,7 @@
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B547" s="2" t="inlineStr">
@@ -31057,7 +31065,7 @@
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B548" s="2" t="inlineStr">
@@ -31072,11 +31080,19 @@
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E548" s="2" t="inlineStr"/>
-      <c r="F548" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>6 strategyclean row(s)</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>6 panel row(s)</t>
+        </is>
+      </c>
       <c r="G548" s="2" t="inlineStr"/>
       <c r="H548" s="2" t="inlineStr"/>
       <c r="I548" s="2" t="inlineStr">
@@ -31088,7 +31104,7 @@
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B549" s="2" t="inlineStr">
@@ -31119,7 +31135,7 @@
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
@@ -31134,11 +31150,19 @@
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E550" s="2" t="inlineStr"/>
-      <c r="F550" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>4 distinct id(s)</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>0 dangle</t>
+        </is>
+      </c>
       <c r="G550" s="2" t="inlineStr"/>
       <c r="H550" s="2" t="inlineStr"/>
       <c r="I550" s="2" t="inlineStr">
@@ -31150,7 +31174,7 @@
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -31165,11 +31189,19 @@
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E551" s="2" t="inlineStr"/>
-      <c r="F551" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>1 metric(s)</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G551" s="2" t="inlineStr"/>
       <c r="H551" s="2" t="inlineStr"/>
       <c r="I551" s="2" t="inlineStr">
@@ -31181,7 +31213,7 @@
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B552" s="2" t="inlineStr">
@@ -31212,7 +31244,7 @@
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
@@ -31237,7 +31269,7 @@
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>0 found</t>
+          <t>1 found</t>
         </is>
       </c>
       <c r="G553" s="2" t="inlineStr"/>
@@ -31251,7 +31283,7 @@
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
@@ -31266,11 +31298,19 @@
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E554" s="2" t="inlineStr"/>
-      <c r="F554" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>0 component(s)</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>0 untraceable</t>
+        </is>
+      </c>
       <c r="G554" s="2" t="inlineStr"/>
       <c r="H554" s="2" t="inlineStr"/>
       <c r="I554" s="2" t="inlineStr">
@@ -31282,7 +31322,7 @@
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B555" s="2" t="inlineStr">
@@ -31321,7 +31361,7 @@
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
@@ -31336,11 +31376,19 @@
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E556" s="2" t="inlineStr"/>
-      <c r="F556" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>6 strategy(ies)</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>0 with no component</t>
+        </is>
+      </c>
       <c r="G556" s="2" t="inlineStr"/>
       <c r="H556" s="2" t="inlineStr"/>
       <c r="I556" s="2" t="inlineStr">
@@ -31352,7 +31400,7 @@
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
@@ -31383,7 +31431,7 @@
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
@@ -31398,11 +31446,19 @@
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E558" s="2" t="inlineStr"/>
-      <c r="F558" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>17 programme(s)</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>0 unreadable (0%), carrying 0% of the money</t>
+        </is>
+      </c>
       <c r="G558" s="2" t="inlineStr"/>
       <c r="H558" s="2" t="inlineStr"/>
       <c r="I558" s="2" t="inlineStr">
@@ -31414,7 +31470,7 @@
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -31445,7 +31501,7 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -31460,11 +31516,19 @@
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E560" s="2" t="inlineStr"/>
-      <c r="F560" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>4 intervention(s) extracted</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>0 uncited (0.0%)</t>
+        </is>
+      </c>
       <c r="G560" s="2" t="inlineStr"/>
       <c r="H560" s="2" t="inlineStr"/>
       <c r="I560" s="2" t="inlineStr">
@@ -31476,7 +31540,7 @@
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>timor_leste</t>
+          <t>thailand_test</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
@@ -31507,7 +31571,7 @@
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -31538,7 +31602,7 @@
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -31569,7 +31633,7 @@
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B564" s="2" t="inlineStr">
@@ -31600,7 +31664,7 @@
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -31631,7 +31695,7 @@
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -31662,7 +31726,7 @@
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B567" s="2" t="inlineStr">
@@ -31693,7 +31757,7 @@
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -31724,7 +31788,7 @@
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B569" s="2" t="inlineStr">
@@ -31755,7 +31819,7 @@
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B570" s="2" t="inlineStr">
@@ -31786,7 +31850,7 @@
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B571" s="2" t="inlineStr">
@@ -31817,7 +31881,7 @@
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B572" s="2" t="inlineStr">
@@ -31848,7 +31912,7 @@
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B573" s="2" t="inlineStr">
@@ -31887,7 +31951,7 @@
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B574" s="2" t="inlineStr">
@@ -31918,7 +31982,7 @@
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B575" s="2" t="inlineStr">
@@ -31957,7 +32021,7 @@
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B576" s="2" t="inlineStr">
@@ -31988,7 +32052,7 @@
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B577" s="2" t="inlineStr">
@@ -32019,7 +32083,7 @@
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B578" s="2" t="inlineStr">
@@ -32050,7 +32114,7 @@
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B579" s="2" t="inlineStr">
@@ -32081,7 +32145,7 @@
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B580" s="2" t="inlineStr">
@@ -32112,7 +32176,7 @@
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>tonga</t>
+          <t>timor_leste</t>
         </is>
       </c>
       <c r="B581" s="2" t="inlineStr">
@@ -32143,7 +32207,7 @@
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B582" s="2" t="inlineStr">
@@ -32174,7 +32238,7 @@
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B583" s="2" t="inlineStr">
@@ -32205,7 +32269,7 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B584" s="2" t="inlineStr">
@@ -32236,7 +32300,7 @@
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B585" s="2" t="inlineStr">
@@ -32267,7 +32331,7 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B586" s="2" t="inlineStr">
@@ -32298,7 +32362,7 @@
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B587" s="2" t="inlineStr">
@@ -32329,7 +32393,7 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B588" s="2" t="inlineStr">
@@ -32360,7 +32424,7 @@
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B589" s="2" t="inlineStr">
@@ -32391,7 +32455,7 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B590" s="2" t="inlineStr">
@@ -32422,7 +32486,7 @@
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B591" s="2" t="inlineStr">
@@ -32453,7 +32517,7 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B592" s="2" t="inlineStr">
@@ -32484,7 +32548,7 @@
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B593" s="2" t="inlineStr">
@@ -32523,7 +32587,7 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B594" s="2" t="inlineStr">
@@ -32554,7 +32618,7 @@
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B595" s="2" t="inlineStr">
@@ -32593,7 +32657,7 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B596" s="2" t="inlineStr">
@@ -32624,7 +32688,7 @@
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B597" s="2" t="inlineStr">
@@ -32655,7 +32719,7 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">
@@ -32686,7 +32750,7 @@
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B599" s="2" t="inlineStr">
@@ -32717,7 +32781,7 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B600" s="2" t="inlineStr">
@@ -32748,7 +32812,7 @@
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>tuvalu</t>
+          <t>tonga</t>
         </is>
       </c>
       <c r="B601" s="2" t="inlineStr">
@@ -32779,7 +32843,7 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B602" s="2" t="inlineStr">
@@ -32810,7 +32874,7 @@
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B603" s="2" t="inlineStr">
@@ -32841,7 +32905,7 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B604" s="2" t="inlineStr">
@@ -32872,7 +32936,7 @@
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B605" s="2" t="inlineStr">
@@ -32903,7 +32967,7 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B606" s="2" t="inlineStr">
@@ -32934,7 +32998,7 @@
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B607" s="2" t="inlineStr">
@@ -32965,7 +33029,7 @@
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B608" s="2" t="inlineStr">
@@ -32996,7 +33060,7 @@
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B609" s="2" t="inlineStr">
@@ -33027,7 +33091,7 @@
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B610" s="2" t="inlineStr">
@@ -33058,7 +33122,7 @@
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B611" s="2" t="inlineStr">
@@ -33089,7 +33153,7 @@
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B612" s="2" t="inlineStr">
@@ -33120,7 +33184,7 @@
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B613" s="2" t="inlineStr">
@@ -33159,7 +33223,7 @@
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B614" s="2" t="inlineStr">
@@ -33190,7 +33254,7 @@
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B615" s="2" t="inlineStr">
@@ -33229,7 +33293,7 @@
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B616" s="2" t="inlineStr">
@@ -33260,7 +33324,7 @@
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B617" s="2" t="inlineStr">
@@ -33291,7 +33355,7 @@
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B618" s="2" t="inlineStr">
@@ -33322,7 +33386,7 @@
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B619" s="2" t="inlineStr">
@@ -33353,7 +33417,7 @@
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B620" s="2" t="inlineStr">
@@ -33384,7 +33448,7 @@
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>vanuatu</t>
+          <t>tuvalu</t>
         </is>
       </c>
       <c r="B621" s="2" t="inlineStr">
@@ -33412,8 +33476,644 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>Stored programme sums</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr"/>
+      <c r="F622" s="2" t="inlineStr"/>
+      <c r="G622" s="2" t="inlineStr"/>
+      <c r="H622" s="2" t="inlineStr"/>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>Stored strategy totals</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr"/>
+      <c r="F623" s="2" t="inlineStr"/>
+      <c r="G623" s="2" t="inlineStr"/>
+      <c r="H623" s="2" t="inlineStr"/>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>Programme counted once</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr"/>
+      <c r="F624" s="2" t="inlineStr"/>
+      <c r="G624" s="2" t="inlineStr"/>
+      <c r="H624" s="2" t="inlineStr"/>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>Ceiling holds</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr"/>
+      <c r="F625" s="2" t="inlineStr"/>
+      <c r="G625" s="2" t="inlineStr"/>
+      <c r="H625" s="2" t="inlineStr"/>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>Panel money matches its edges</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr"/>
+      <c r="F626" s="2" t="inlineStr"/>
+      <c r="G626" s="2" t="inlineStr"/>
+      <c r="H626" s="2" t="inlineStr"/>
+      <c r="I626" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>Edges cite real programmes</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr"/>
+      <c r="F627" s="2" t="inlineStr"/>
+      <c r="G627" s="2" t="inlineStr"/>
+      <c r="H627" s="2" t="inlineStr"/>
+      <c r="I627" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>No strategy dropped</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr"/>
+      <c r="F628" s="2" t="inlineStr"/>
+      <c r="G628" s="2" t="inlineStr"/>
+      <c r="H628" s="2" t="inlineStr"/>
+      <c r="I628" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>Unfunded list is complete</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr"/>
+      <c r="F629" s="2" t="inlineStr"/>
+      <c r="G629" s="2" t="inlineStr"/>
+      <c r="H629" s="2" t="inlineStr"/>
+      <c r="I629" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>Evidence chain resolves</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr"/>
+      <c r="F630" s="2" t="inlineStr"/>
+      <c r="G630" s="2" t="inlineStr"/>
+      <c r="H630" s="2" t="inlineStr"/>
+      <c r="I630" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>Maturity summary is derivable</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr"/>
+      <c r="F631" s="2" t="inlineStr"/>
+      <c r="G631" s="2" t="inlineStr"/>
+      <c r="H631" s="2" t="inlineStr"/>
+      <c r="I631" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>No duplicate edges</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr"/>
+      <c r="F632" s="2" t="inlineStr"/>
+      <c r="G632" s="2" t="inlineStr"/>
+      <c r="H632" s="2" t="inlineStr"/>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>One currency</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>1 expected</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G633" s="2" t="inlineStr"/>
+      <c r="H633" s="2" t="inlineStr"/>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>Components are traceable</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr"/>
+      <c r="F634" s="2" t="inlineStr"/>
+      <c r="G634" s="2" t="inlineStr"/>
+      <c r="H634" s="2" t="inlineStr"/>
+      <c r="I634" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>No workbook open in Excel</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>0 expected</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G635" s="2" t="inlineStr"/>
+      <c r="H635" s="2" t="inlineStr"/>
+      <c r="I635" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>Strategies come from the plan</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr"/>
+      <c r="F636" s="2" t="inlineStr"/>
+      <c r="G636" s="2" t="inlineStr"/>
+      <c r="H636" s="2" t="inlineStr"/>
+      <c r="I636" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>Funding priority is reproducible</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr"/>
+      <c r="F637" s="2" t="inlineStr"/>
+      <c r="G637" s="2" t="inlineStr"/>
+      <c r="H637" s="2" t="inlineStr"/>
+      <c r="I637" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>The budget is readable</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr"/>
+      <c r="F638" s="2" t="inlineStr"/>
+      <c r="G638" s="2" t="inlineStr"/>
+      <c r="H638" s="2" t="inlineStr"/>
+      <c r="I638" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous codes name their head</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr"/>
+      <c r="F639" s="2" t="inlineStr"/>
+      <c r="G639" s="2" t="inlineStr"/>
+      <c r="H639" s="2" t="inlineStr"/>
+      <c r="I639" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>Every intervention is traceable to a strategy</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr"/>
+      <c r="F640" s="2" t="inlineStr"/>
+      <c r="G640" s="2" t="inlineStr"/>
+      <c r="H640" s="2" t="inlineStr"/>
+      <c r="I640" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>vanuatu</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>The sector layer stayed out of the panel</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr"/>
+      <c r="F641" s="2" t="inlineStr"/>
+      <c r="G641" s="2" t="inlineStr"/>
+      <c r="H641" s="2" t="inlineStr"/>
+      <c r="I641" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I621"/>
+  <autoFilter ref="A1:I641"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33508,12 +34208,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>colombia;egypt;ethiopia;iran;kazakhstan;laos;marshall_islands;mongolia;morocco;myanmar;nepal;nigeria;pakistan;palau;peru;philippines;serbia;solomon_islands;timor_leste;tonga;tuvalu;uzbekistan;vanuatu;vietnam</t>
+          <t>colombia;egypt;ethiopia;iran;kazakhstan;laos;marshall_islands;morocco;myanmar;nepal;nigeria;pakistan;palau;peru;philippines;serbia;solomon_islands;timor_leste;tonga;tuvalu;uzbekistan;vanuatu;vietnam</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -33536,7 +34236,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>cambodia;indonesia</t>
+          <t>cambodia;indonesia;mongolia</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/DATA_AUDIT.xlsx
+++ b/DATA_AUDIT.xlsx
@@ -435,8 +435,8 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="67" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
     <col width="68" customWidth="1" min="7" max="7"/>
     <col width="90" customWidth="1" min="8" max="8"/>
   </cols>
@@ -582,16 +582,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -616,16 +624,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -810,16 +826,24 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -844,16 +868,24 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL (advisory)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 COULD NOT RUN [advisory]</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1030,16 +1062,24 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 4 FAIL - 1 input(s) not on this machine</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1064,16 +1104,24 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 3 FAIL - 1 COULD NOT RUN - 1 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1494,16 +1542,24 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>PASS 0/4 - 4 FAIL</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1528,16 +1584,24 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>PASS 0/4 - 4 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1727,7 +1791,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1761,7 +1825,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1908,24 +1972,16 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 FAIL</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
-        </is>
-      </c>
+          <t>PASS 1/1</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1950,16 +2006,24 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1984,16 +2048,24 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2926,16 +2998,24 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+          <t>PASS 0/14 - 8 FAIL - 6 input(s) not on this machine</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2960,16 +3040,24 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
+          <t>PASS 0/14 - 8 FAIL - 6 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3120,24 +3208,16 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 FAIL</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
-        </is>
-      </c>
+          <t>PASS 1/1</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3162,16 +3242,24 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
+          <t>PASS 0/3 - 3 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3196,16 +3284,24 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
+          <t>PASS 0/3 - 3 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3398,16 +3494,24 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
+          <t>PASS 1/8 - 5 FAIL - 2 COULD NOT RUN</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3432,16 +3536,24 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
+          <t>PASS 0/8 - 5 FAIL - 3 COULD NOT RUN [advisory]</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3867,7 +3979,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/3 - 3 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -3901,7 +4013,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/3 - 3 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
@@ -4090,16 +4202,24 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
+          <t>PASS 0/3 - 3 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4129,7 +4249,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 3/3 [advisory]</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
@@ -4570,16 +4690,24 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
+          <t>PASS 1/3 - 1 FAIL - 1 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4604,16 +4732,24 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
+          <t>PASS 0/3 - 2 FAIL - 1 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4806,16 +4942,24 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
+          <t>PASS 2/7 - 5 FAIL</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4840,16 +4984,24 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr"/>
+          <t>PASS 0/7 - 5 FAIL - 2 COULD NOT RUN [advisory]</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5278,16 +5430,24 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5312,16 +5472,24 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5514,16 +5682,24 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr"/>
+          <t>PASS 0/16 - 11 FAIL - 5 input(s) not on this machine</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5548,16 +5724,24 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr"/>
+          <t>PASS 0/16 - 9 FAIL - 2 COULD NOT RUN - 5 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5739,7 +5923,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
@@ -5773,7 +5957,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
@@ -6686,16 +6870,24 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
+          <t>PASS 0/2 - 1 FAIL - 1 input(s) not on this machine</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6720,16 +6912,24 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL (advisory)</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr"/>
+          <t>PASS 0/2 - 1 COULD NOT RUN - 1 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6914,16 +7114,24 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6948,16 +7156,24 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 5 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -7391,7 +7607,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/1 - 1 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
@@ -7425,7 +7641,7 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/1 - 1 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
@@ -7611,7 +7827,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/3 - 3 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
@@ -7645,7 +7861,7 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/3 - 3 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
@@ -7800,24 +8016,16 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 FAIL</t>
-        </is>
-      </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr">
-        <is>
-          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
-        </is>
-      </c>
+          <t>PASS 1/1</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -7842,16 +8050,24 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr"/>
+          <t>PASS 1/7 - 2 FAIL - 4 input(s) not on this machine</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -7876,16 +8092,24 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr"/>
+          <t>PASS 0/7 - 3 FAIL - 4 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -8319,7 +8543,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/3 - 3 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
@@ -8353,7 +8577,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/3 - 3 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr"/>
@@ -8542,16 +8766,24 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr"/>
+          <t>PASS 1/3 - 2 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -8576,16 +8808,24 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr"/>
+          <t>PASS 1/3 - 2 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -8770,16 +9010,24 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 2 FAIL - 3 COULD NOT RUN</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -8804,16 +9052,24 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 2 FAIL - 3 COULD NOT RUN [advisory]</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -9250,16 +9506,24 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 4 FAIL - 1 COULD NOT RUN</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -9284,16 +9548,24 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr"/>
+          <t>PASS 0/5 - 3 FAIL - 2 COULD NOT RUN [advisory]</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -9470,16 +9742,24 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr"/>
+          <t>PASS 1/4 - 3 FAIL [advisory]</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -9504,16 +9784,24 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
+          <t>PASS 0/4 - 3 FAIL - 1 COULD NOT RUN [advisory]</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -9656,24 +9944,16 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 FAIL</t>
-        </is>
-      </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>stage 6 or 6b cites a programme or strategy the inputs do not hold</t>
-        </is>
-      </c>
-      <c r="H237" s="2" t="inlineStr">
-        <is>
-          <t>validation/refs_*.xlsx names each dangling reference; re-run the mapping for that year</t>
-        </is>
-      </c>
+          <t>PASS 1/1</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -9779,7 +10059,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>PASS 1/1</t>
+          <t>PASS 0/1 - 1 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr"/>
@@ -9918,16 +10198,24 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 input(s) not on this machine</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr"/>
+          <t>PASS 0/1 - 1 FAIL</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -9957,7 +10245,7 @@
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>PASS 0/1 - 1 input(s) not on this machine [advisory]</t>
+          <t>PASS 1/1 [advisory]</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr"/>
@@ -10143,7 +10431,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/6 - 6 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr"/>
@@ -10177,7 +10465,7 @@
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/6 - 6 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr"/>
@@ -10363,7 +10651,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr"/>
@@ -10397,7 +10685,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr"/>
@@ -10586,16 +10874,24 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr"/>
+          <t>PASS 0/8 - 3 COULD NOT RUN - 5 input(s) not on this machine</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 emitted an amount or code the source PDF does not contain</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>validation/fidelity_*.xlsx names the row; check the page, then re-run stage 5 with a page-range hint</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -10620,16 +10916,24 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL (advisory)</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
-        </is>
-      </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr"/>
+          <t>PASS 0/8 - 3 COULD NOT RUN - 5 input(s) not on this machine [advisory]</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>stage 5 missed programme rows the source contains</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>validation/recall_*.xlsx lists the candidates; widen the page range or split the document</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -11063,7 +11367,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr"/>
@@ -11097,7 +11401,7 @@
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>NOT CONFIGURED - this figure was never checked against the source</t>
+          <t>PASS 0/5 - 5 input(s) not on this machine [advisory]</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr"/>
@@ -11443,8 +11747,8 @@
     <col width="47" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="90" customWidth="1" min="8" max="8"/>
     <col width="90" customWidth="1" min="9" max="9"/>
   </cols>
@@ -11519,7 +11823,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>432 strategy-year(s)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -11558,7 +11862,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>11 strategy-year(s)</t>
+          <t>432 strategy-year(s)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -11929,7 +12233,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1 found</t>
+          <t>0 found</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -12643,7 +12947,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -12653,22 +12957,14 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2 found</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>the config, currency_unit</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
-        </is>
-      </c>
+          <t>0 found</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>["Crore Tk.", "crore Taka"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -12975,7 +13271,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>210 strategy-year(s)</t>
+          <t>238 strategy-year(s)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -13014,7 +13310,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>210 strategy-year(s)</t>
+          <t>238 strategy-year(s)</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -13567,7 +13863,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>92 programme(s)</t>
+          <t>148 programme(s)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -15879,7 +16175,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>8 strategy-year(s)</t>
+          <t>29 strategy-year(s)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -15918,7 +16214,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>8 strategy-year(s)</t>
+          <t>15 strategy-year(s)</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -16279,7 +16575,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -16289,22 +16585,14 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2 found</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>the config, currency_unit</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
-        </is>
-      </c>
+          <t>1 found</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>["CNY billion", "yuan"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -16479,19 +16767,19 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>17 programme(s)</t>
+          <t>130 programme(s)</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>0 unreadable (0%), carrying 0% of the money</t>
+          <t>14 unreadable (11%), carrying 29% of the money</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["FY2025 : ''", "FY2025 : ''", "FY2025 : ''", "FY2025 : ''", "FY2025 : ''", "FY2025 : ''", "FY2025 : ''", "FY2025 : ''"]</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16907,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>19 strategy-year(s)</t>
+          <t>33 strategy-year(s)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -17223,7 +17511,7 @@
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>["FY2018 None: 'None'", "FY2018 None: 'None'", "FY2018 None: 'None'", "FY2018 None: 'None'", "FY2018 None: 'None'", "FY2018 None: 'None'", "FY2018 None: 'None'", "FY2018 None: 'None'"]</t>
+          <t>["FY2018 : ''", "FY2018 : ''", "FY2018 : ''", "FY2018 : ''", "FY2018 : ''", "FY2018 : ''", "FY2018 : ''", "FY2018 : ''"]</t>
         </is>
       </c>
     </row>
@@ -17351,7 +17639,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>261 strategy-year(s)</t>
+          <t>146 strategy-year(s)</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -17390,7 +17678,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>261 strategy-year(s)</t>
+          <t>145 strategy-year(s)</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -17943,7 +18231,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>124 programme(s)</t>
+          <t>190 programme(s)</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -18083,7 +18371,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>1 strategy-year(s)</t>
+          <t>299 strategy-year(s)</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -18122,7 +18410,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>1 strategy-year(s)</t>
+          <t>267 strategy-year(s)</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -18683,7 +18971,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>13 programme(s)</t>
+          <t>1362 programme(s)</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -19507,7 +19795,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>79 strategy-year(s)</t>
+          <t>123 strategy-year(s)</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -20273,32 +20561,24 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>393 strategy-year(s)</t>
+          <t>389 strategy-year(s)</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>4 disagree</t>
-        </is>
-      </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>stage 5: the head's own printed total</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>compare the strategy_total row to the document; a wrong read is a stage 5 re-run, a wrong unit is scale.py</t>
-        </is>
-      </c>
+          <t>0 disagree</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>["FY2020 strategy 0703000: stored 0.0, layer -", "FY2020 strategy 0740000: stored 0.0, layer -", "FY2020 strategy 1008000: stored 0.0, layer -", "FY2020 strategy 1014000: stored 0.0, layer -"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -20987,7 +21267,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>81 strategy-year(s)</t>
+          <t>135 strategy-year(s)</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
@@ -21021,32 +21301,24 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>81 strategy-year(s)</t>
+          <t>127 strategy-year(s)</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>1 disagree</t>
-        </is>
-      </c>
-      <c r="G263" s="2" t="inlineStr">
-        <is>
-          <t>stage 5: the head's own printed total</t>
-        </is>
-      </c>
-      <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>compare the strategy_total row to the document; a wrong read is a stage 5 re-run, a wrong unit is scale.py</t>
-        </is>
-      </c>
+          <t>0 disagree</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>["FY2026 strategy 03: stored 0.0, layer -"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -21587,19 +21859,19 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>215 programme(s)</t>
+          <t>654 programme(s)</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>0 unreadable (0%), carrying 0% of the money</t>
+          <t>2 unreadable (0%), carrying 0% of the money</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr"/>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["FY2021 25.07: 'IT'", "FY2021 29.07: 'IT'"]</t>
         </is>
       </c>
     </row>
@@ -22475,7 +22747,7 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>384 strategy-year(s)</t>
+          <t>487 strategy-year(s)</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
@@ -22509,32 +22781,24 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>384 strategy-year(s)</t>
+          <t>473 strategy-year(s)</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>11 disagree</t>
-        </is>
-      </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>stage 5: the head's own printed total</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="inlineStr">
-        <is>
-          <t>compare the strategy_total row to the document; a wrong read is a stage 5 re-run, a wrong unit is scale.py</t>
-        </is>
-      </c>
+          <t>0 disagree</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>["FY2008 strategy 3: stored 0.0, layer -", "FY2008 strategy 12: stored 0.0, layer -", "FY2008 strategy 25: stored 0.0, layer -", "FY2008 strategy 26: stored 0.0, layer -", "FY2011 strategy 3: stored 0.0, layer -", "FY2014 strategy 19: stored 0.0, layer -", "FY2015 strategy 37: stored 0.0, layer -", "FY2015 strategy 38: stored 0.0, layer -"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -23083,7 +23347,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2844 programme(s)</t>
+          <t>3536 programme(s)</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -23879,11 +24143,19 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E341" s="2" t="inlineStr"/>
-      <c r="F341" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>204 sector intervention(s) not in the plan</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>0 of them present in the panel</t>
+        </is>
+      </c>
       <c r="G341" s="2" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr"/>
       <c r="I341" s="2" t="inlineStr">
@@ -24618,11 +24890,19 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E362" s="2" t="inlineStr"/>
-      <c r="F362" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>91 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G362" s="2" t="inlineStr"/>
       <c r="H362" s="2" t="inlineStr"/>
       <c r="I362" s="2" t="inlineStr">
@@ -24649,11 +24929,19 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E363" s="2" t="inlineStr"/>
-      <c r="F363" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>63 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G363" s="2" t="inlineStr"/>
       <c r="H363" s="2" t="inlineStr"/>
       <c r="I363" s="2" t="inlineStr">
@@ -25146,16 +25434,24 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr"/>
-      <c r="F378" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>482 programme(s)</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>28 unreadable (6%), carrying 6% of the money</t>
+        </is>
+      </c>
       <c r="G378" s="2" t="inlineStr"/>
       <c r="H378" s="2" t="inlineStr"/>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["FY2024 : ''", "FY2024 : ''", "FY2024 : ''", "FY2024 : ''", "FY2024 : ''", "FY2024 : ''", "FY2024 : ''", "FY2024 : ''"]</t>
         </is>
       </c>
     </row>
@@ -26547,7 +26843,7 @@
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>22 strategy-year(s)</t>
+          <t>104 strategy-year(s)</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr">
@@ -26586,7 +26882,7 @@
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>22 strategy-year(s)</t>
+          <t>104 strategy-year(s)</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -27139,7 +27435,7 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>48 programme(s)</t>
+          <t>159 programme(s)</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
@@ -27243,11 +27539,19 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E441" s="2" t="inlineStr"/>
-      <c r="F441" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>497 sector intervention(s) not in the plan</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>0 of them present in the panel</t>
+        </is>
+      </c>
       <c r="G441" s="2" t="inlineStr"/>
       <c r="H441" s="2" t="inlineStr"/>
       <c r="I441" s="2" t="inlineStr">
@@ -28011,7 +28315,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>83 strategy-year(s)</t>
+          <t>36 strategy-year(s)</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
@@ -28050,7 +28354,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>83 strategy-year(s)</t>
+          <t>36 strategy-year(s)</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -28603,7 +28907,7 @@
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>191 programme(s)</t>
+          <t>143 programme(s)</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
@@ -28738,11 +29042,19 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E482" s="2" t="inlineStr"/>
-      <c r="F482" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>8 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G482" s="2" t="inlineStr"/>
       <c r="H482" s="2" t="inlineStr"/>
       <c r="I482" s="2" t="inlineStr">
@@ -28769,11 +29081,19 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E483" s="2" t="inlineStr"/>
-      <c r="F483" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>8 strategy-year(s)</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>0 disagree</t>
+        </is>
+      </c>
       <c r="G483" s="2" t="inlineStr"/>
       <c r="H483" s="2" t="inlineStr"/>
       <c r="I483" s="2" t="inlineStr">
@@ -29266,11 +29586,19 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E498" s="2" t="inlineStr"/>
-      <c r="F498" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>83 programme(s)</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>0 unreadable (0%), carrying 0% of the money</t>
+        </is>
+      </c>
       <c r="G498" s="2" t="inlineStr"/>
       <c r="H498" s="2" t="inlineStr"/>
       <c r="I498" s="2" t="inlineStr">
@@ -29395,7 +29723,7 @@
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>50 strategy-year(s)</t>
+          <t>6 strategy-year(s)</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -29434,7 +29762,7 @@
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>50 strategy-year(s)</t>
+          <t>5 strategy-year(s)</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
@@ -29795,7 +30123,7 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -29805,22 +30133,14 @@
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>2 found</t>
-        </is>
-      </c>
-      <c r="G513" s="2" t="inlineStr">
-        <is>
-          <t>the config, currency_unit</t>
-        </is>
-      </c>
-      <c r="H513" s="2" t="inlineStr">
-        <is>
-          <t>one currency per country: fix currency_unit in configs/&lt;slug&gt;.json or the unit a budget file states</t>
-        </is>
-      </c>
+          <t>1 found</t>
+        </is>
+      </c>
+      <c r="G513" s="2" t="inlineStr"/>
+      <c r="H513" s="2" t="inlineStr"/>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>["Rs. Billion", "Rs.Mn"]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -29990,11 +30310,19 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr"/>
-      <c r="F518" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>140 programme(s)</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>0 unreadable (0%), carrying 0% of the money</t>
+        </is>
+      </c>
       <c r="G518" s="2" t="inlineStr"/>
       <c r="H518" s="2" t="inlineStr"/>
       <c r="I518" s="2" t="inlineStr">
@@ -30127,7 +30455,7 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year(s)</t>
+          <t>35 strategy-year(s)</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -30166,7 +30494,7 @@
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>28 strategy-year(s)</t>
+          <t>35 strategy-year(s)</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -30719,7 +31047,7 @@
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>273 programme(s)</t>
+          <t>367 programme(s)</t>
         </is>
       </c>
       <c r="F538" s="2" t="inlineStr">
@@ -30823,11 +31151,19 @@
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>SKIPPED</t>
-        </is>
-      </c>
-      <c r="E541" s="2" t="inlineStr"/>
-      <c r="F541" s="2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>660 sector intervention(s) not in the plan</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>0 of them present in the panel</t>
+        </is>
+      </c>
       <c r="G541" s="2" t="inlineStr"/>
       <c r="H541" s="2" t="inlineStr"/>
       <c r="I541" s="2" t="inlineStr">
@@ -34754,12 +35090,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -34796,17 +35132,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -34890,17 +35226,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>383</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -35036,12 +35372,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -35449,12 +35785,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -35464,7 +35800,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
